--- a/Interpolate IBI data/IBIS statistics post interpolation_Moritz.xlsx
+++ b/Interpolate IBI data/IBIS statistics post interpolation_Moritz.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123.633</v>
+        <v>247.266</v>
       </c>
       <c r="D2" t="n">
         <v>565</v>
       </c>
       <c r="E2" t="n">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="F2" t="n">
-        <v>218.1610619469027</v>
+        <v>436.3221238938053</v>
       </c>
       <c r="G2" t="n">
-        <v>21.62069632339734</v>
+        <v>43.24139264679467</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -510,19 +510,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>149.88</v>
+        <v>299.76</v>
       </c>
       <c r="D3" t="n">
         <v>666</v>
       </c>
       <c r="E3" t="n">
-        <v>223</v>
+        <v>446</v>
       </c>
       <c r="F3" t="n">
-        <v>224.7972972972973</v>
+        <v>449.5945945945946</v>
       </c>
       <c r="G3" t="n">
-        <v>13.75169901383536</v>
+        <v>27.50339802767073</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>132.283</v>
+        <v>264.566</v>
       </c>
       <c r="D4" t="n">
         <v>574</v>
       </c>
       <c r="E4" t="n">
-        <v>231</v>
+        <v>462</v>
       </c>
       <c r="F4" t="n">
-        <v>229.8519163763066</v>
+        <v>459.7038327526133</v>
       </c>
       <c r="G4" t="n">
-        <v>12.68413507236528</v>
+        <v>25.36827014473057</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>149.898</v>
+        <v>299.796</v>
       </c>
       <c r="D5" t="n">
         <v>730</v>
       </c>
       <c r="E5" t="n">
-        <v>204</v>
+        <v>408</v>
       </c>
       <c r="F5" t="n">
-        <v>205.1</v>
+        <v>410.2</v>
       </c>
       <c r="G5" t="n">
-        <v>8.024285839706321</v>
+        <v>16.04857167941264</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -600,19 +600,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>150.124</v>
+        <v>300.248</v>
       </c>
       <c r="D6" t="n">
         <v>628</v>
       </c>
       <c r="E6" t="n">
-        <v>243.5</v>
+        <v>487</v>
       </c>
       <c r="F6" t="n">
-        <v>238.5652866242038</v>
+        <v>477.1305732484076</v>
       </c>
       <c r="G6" t="n">
-        <v>21.45364511577091</v>
+        <v>42.90729023154183</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>126.453</v>
+        <v>252.906</v>
       </c>
       <c r="D7" t="n">
         <v>591</v>
       </c>
       <c r="E7" t="n">
-        <v>207</v>
+        <v>414</v>
       </c>
       <c r="F7" t="n">
-        <v>213.4720812182741</v>
+        <v>426.9441624365482</v>
       </c>
       <c r="G7" t="n">
-        <v>41.58530724357516</v>
+        <v>83.17061448715032</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.366</v>
+        <v>182.732</v>
       </c>
       <c r="D8" t="n">
         <v>254</v>
       </c>
       <c r="E8" t="n">
-        <v>358</v>
+        <v>716</v>
       </c>
       <c r="F8" t="n">
-        <v>359.0629921259842</v>
+        <v>718.1259842519685</v>
       </c>
       <c r="G8" t="n">
-        <v>34.41211479648899</v>
+        <v>68.82422959297797</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150.405</v>
+        <v>300.81</v>
       </c>
       <c r="D9" t="n">
         <v>719</v>
       </c>
       <c r="E9" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="F9" t="n">
-        <v>208.9596662030598</v>
+        <v>417.9193324061196</v>
       </c>
       <c r="G9" t="n">
-        <v>13.16934009551644</v>
+        <v>26.33868019103289</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149.958</v>
+        <v>299.916</v>
       </c>
       <c r="D10" t="n">
         <v>624</v>
       </c>
       <c r="E10" t="n">
-        <v>239</v>
+        <v>478</v>
       </c>
       <c r="F10" t="n">
-        <v>240.0753205128205</v>
+        <v>480.1506410256411</v>
       </c>
       <c r="G10" t="n">
-        <v>20.58102493504739</v>
+        <v>41.16204987009478</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>110.412</v>
+        <v>220.824</v>
       </c>
       <c r="D11" t="n">
         <v>428</v>
       </c>
       <c r="E11" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="F11" t="n">
-        <v>257.1985981308411</v>
+        <v>514.3971962616822</v>
       </c>
       <c r="G11" t="n">
-        <v>39.15226144789714</v>
+        <v>78.30452289579428</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>150.089</v>
+        <v>300.178</v>
       </c>
       <c r="D12" t="n">
         <v>670</v>
       </c>
       <c r="E12" t="n">
-        <v>224</v>
+        <v>448</v>
       </c>
       <c r="F12" t="n">
-        <v>223.7373134328358</v>
+        <v>447.4746268656717</v>
       </c>
       <c r="G12" t="n">
-        <v>13.85952194436829</v>
+        <v>27.71904388873658</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -810,19 +810,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>150.039</v>
+        <v>300.078</v>
       </c>
       <c r="D13" t="n">
         <v>684</v>
       </c>
       <c r="E13" t="n">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="F13" t="n">
-        <v>218.9415204678363</v>
+        <v>437.8830409356725</v>
       </c>
       <c r="G13" t="n">
-        <v>19.00564995823258</v>
+        <v>38.01129991646516</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>149.846</v>
+        <v>299.692</v>
       </c>
       <c r="D14" t="n">
         <v>646</v>
       </c>
       <c r="E14" t="n">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="F14" t="n">
-        <v>231.484520123839</v>
+        <v>462.969040247678</v>
       </c>
       <c r="G14" t="n">
-        <v>17.75576531333936</v>
+        <v>35.51153062667871</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>98.547</v>
+        <v>197.094</v>
       </c>
       <c r="D15" t="n">
         <v>474</v>
       </c>
       <c r="E15" t="n">
-        <v>204</v>
+        <v>408</v>
       </c>
       <c r="F15" t="n">
-        <v>207.4725738396625</v>
+        <v>414.9451476793249</v>
       </c>
       <c r="G15" t="n">
-        <v>36.54179290729061</v>
+        <v>73.08358581458121</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>149.857</v>
+        <v>299.714</v>
       </c>
       <c r="D16" t="n">
         <v>693</v>
       </c>
       <c r="E16" t="n">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="F16" t="n">
-        <v>215.7604617604618</v>
+        <v>431.5209235209235</v>
       </c>
       <c r="G16" t="n">
-        <v>25.06547024554696</v>
+        <v>50.13094049109392</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -930,19 +930,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>150.18</v>
+        <v>300.36</v>
       </c>
       <c r="D17" t="n">
         <v>648</v>
       </c>
       <c r="E17" t="n">
-        <v>231</v>
+        <v>462</v>
       </c>
       <c r="F17" t="n">
-        <v>231.3024691358025</v>
+        <v>462.604938271605</v>
       </c>
       <c r="G17" t="n">
-        <v>15.45621107075249</v>
+        <v>30.91242214150498</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>150.068</v>
+        <v>300.136</v>
       </c>
       <c r="D18" t="n">
         <v>591</v>
       </c>
       <c r="E18" t="n">
-        <v>253</v>
+        <v>506</v>
       </c>
       <c r="F18" t="n">
-        <v>253.6412859560068</v>
+        <v>507.2825719120135</v>
       </c>
       <c r="G18" t="n">
-        <v>15.05987781157093</v>
+        <v>30.11975562314186</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -990,19 +990,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>150.09</v>
+        <v>300.18</v>
       </c>
       <c r="D19" t="n">
         <v>668</v>
       </c>
       <c r="E19" t="n">
-        <v>226</v>
+        <v>452</v>
       </c>
       <c r="F19" t="n">
-        <v>224.4251497005988</v>
+        <v>448.8502994011976</v>
       </c>
       <c r="G19" t="n">
-        <v>15.42303314046621</v>
+        <v>30.84606628093241</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1020,19 +1020,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>149.986</v>
+        <v>299.972</v>
       </c>
       <c r="D20" t="n">
         <v>621</v>
       </c>
       <c r="E20" t="n">
-        <v>239</v>
+        <v>478</v>
       </c>
       <c r="F20" t="n">
-        <v>241.2447665056361</v>
+        <v>482.4895330112722</v>
       </c>
       <c r="G20" t="n">
-        <v>17.93423449498748</v>
+        <v>35.86846898997496</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1050,19 +1050,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>150.13</v>
+        <v>300.26</v>
       </c>
       <c r="D21" t="n">
         <v>717</v>
       </c>
       <c r="E21" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="F21" t="n">
-        <v>209.0153417015342</v>
+        <v>418.0306834030683</v>
       </c>
       <c r="G21" t="n">
-        <v>17.20647010474488</v>
+        <v>34.41294020948975</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>150.121</v>
+        <v>300.242</v>
       </c>
       <c r="D22" t="n">
         <v>662</v>
       </c>
       <c r="E22" t="n">
-        <v>226</v>
+        <v>452</v>
       </c>
       <c r="F22" t="n">
-        <v>226.3716012084592</v>
+        <v>452.7432024169185</v>
       </c>
       <c r="G22" t="n">
-        <v>23.29780190337869</v>
+        <v>46.59560380675738</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>150.091</v>
+        <v>300.182</v>
       </c>
       <c r="D23" t="n">
         <v>654</v>
       </c>
       <c r="E23" t="n">
-        <v>227</v>
+        <v>454</v>
       </c>
       <c r="F23" t="n">
-        <v>228.9250764525994</v>
+        <v>457.8501529051988</v>
       </c>
       <c r="G23" t="n">
-        <v>15.93446228876659</v>
+        <v>31.86892457753318</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1140,19 +1140,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>150.1</v>
+        <v>300.2</v>
       </c>
       <c r="D24" t="n">
         <v>678</v>
       </c>
       <c r="E24" t="n">
-        <v>221</v>
+        <v>442</v>
       </c>
       <c r="F24" t="n">
-        <v>220.9911504424779</v>
+        <v>441.9823008849557</v>
       </c>
       <c r="G24" t="n">
-        <v>14.75190931751024</v>
+        <v>29.50381863502049</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>149.903</v>
+        <v>299.806</v>
       </c>
       <c r="D25" t="n">
         <v>704</v>
       </c>
       <c r="E25" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="F25" t="n">
-        <v>212.5539772727273</v>
+        <v>425.1079545454546</v>
       </c>
       <c r="G25" t="n">
-        <v>23.95841432900396</v>
+        <v>47.91682865800792</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>149.776</v>
+        <v>299.552</v>
       </c>
       <c r="D26" t="n">
         <v>567</v>
       </c>
       <c r="E26" t="n">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="F26" t="n">
-        <v>263.6067019400353</v>
+        <v>527.2134038800706</v>
       </c>
       <c r="G26" t="n">
-        <v>28.94094433309958</v>
+        <v>57.88188866619917</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>150.115</v>
+        <v>300.23</v>
       </c>
       <c r="D27" t="n">
         <v>620</v>
       </c>
       <c r="E27" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="F27" t="n">
-        <v>241.6209677419355</v>
+        <v>483.241935483871</v>
       </c>
       <c r="G27" t="n">
-        <v>14.72131681237774</v>
+        <v>29.44263362475548</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1260,19 +1260,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>150.116</v>
+        <v>300.232</v>
       </c>
       <c r="D28" t="n">
         <v>681</v>
       </c>
       <c r="E28" t="n">
-        <v>218</v>
+        <v>436</v>
       </c>
       <c r="F28" t="n">
-        <v>219.9676945668135</v>
+        <v>439.935389133627</v>
       </c>
       <c r="G28" t="n">
-        <v>15.61010651509001</v>
+        <v>31.22021303018003</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1290,19 +1290,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>112.285</v>
+        <v>224.57</v>
       </c>
       <c r="D29" t="n">
         <v>556</v>
       </c>
       <c r="E29" t="n">
-        <v>202</v>
+        <v>404</v>
       </c>
       <c r="F29" t="n">
-        <v>201.5989208633094</v>
+        <v>403.1978417266187</v>
       </c>
       <c r="G29" t="n">
-        <v>20.06949903774776</v>
+        <v>40.13899807549553</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>149.944</v>
+        <v>299.888</v>
       </c>
       <c r="D30" t="n">
         <v>599</v>
       </c>
       <c r="E30" t="n">
-        <v>249</v>
+        <v>498</v>
       </c>
       <c r="F30" t="n">
-        <v>249.7696160267112</v>
+        <v>499.5392320534224</v>
       </c>
       <c r="G30" t="n">
-        <v>20.80295382822854</v>
+        <v>41.60590765645707</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1350,19 +1350,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>147.485</v>
+        <v>294.97</v>
       </c>
       <c r="D31" t="n">
         <v>674</v>
       </c>
       <c r="E31" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F31" t="n">
-        <v>218.540059347181</v>
+        <v>437.080118694362</v>
       </c>
       <c r="G31" t="n">
-        <v>27.56522505062437</v>
+        <v>55.13045010124874</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>150.077</v>
+        <v>300.154</v>
       </c>
       <c r="D32" t="n">
         <v>643</v>
       </c>
       <c r="E32" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F32" t="n">
-        <v>232.9315707620529</v>
+        <v>465.8631415241057</v>
       </c>
       <c r="G32" t="n">
-        <v>16.56089438763111</v>
+        <v>33.12178877526222</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1410,19 +1410,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>150.127</v>
+        <v>300.254</v>
       </c>
       <c r="D33" t="n">
         <v>609</v>
       </c>
       <c r="E33" t="n">
-        <v>246</v>
+        <v>492</v>
       </c>
       <c r="F33" t="n">
-        <v>246.1510673234811</v>
+        <v>492.3021346469623</v>
       </c>
       <c r="G33" t="n">
-        <v>23.88480102651166</v>
+        <v>47.76960205302331</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1440,19 +1440,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>150.09</v>
+        <v>300.18</v>
       </c>
       <c r="D34" t="n">
         <v>639</v>
       </c>
       <c r="E34" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F34" t="n">
-        <v>234.564945226917</v>
+        <v>469.1298904538341</v>
       </c>
       <c r="G34" t="n">
-        <v>15.09681684841793</v>
+        <v>30.19363369683586</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1470,19 +1470,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>150.05</v>
+        <v>300.1</v>
       </c>
       <c r="D35" t="n">
         <v>608</v>
       </c>
       <c r="E35" t="n">
-        <v>247</v>
+        <v>494</v>
       </c>
       <c r="F35" t="n">
-        <v>246.3256578947368</v>
+        <v>492.6513157894737</v>
       </c>
       <c r="G35" t="n">
-        <v>30.37181776299757</v>
+        <v>60.74363552599514</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1500,19 +1500,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>150.053</v>
+        <v>300.106</v>
       </c>
       <c r="D36" t="n">
         <v>562</v>
       </c>
       <c r="E36" t="n">
-        <v>246</v>
+        <v>492</v>
       </c>
       <c r="F36" t="n">
-        <v>266.4074733096085</v>
+        <v>532.814946619217</v>
       </c>
       <c r="G36" t="n">
-        <v>67.52116837958454</v>
+        <v>135.0423367591691</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1530,19 +1530,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>147.583</v>
+        <v>295.166</v>
       </c>
       <c r="D37" t="n">
         <v>556</v>
       </c>
       <c r="E37" t="n">
-        <v>261</v>
+        <v>522</v>
       </c>
       <c r="F37" t="n">
-        <v>264.1978417266187</v>
+        <v>528.3956834532374</v>
       </c>
       <c r="G37" t="n">
-        <v>33.96082102515827</v>
+        <v>67.92164205031655</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>150.146</v>
+        <v>300.292</v>
       </c>
       <c r="D38" t="n">
         <v>654</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="F38" t="n">
-        <v>229.0917431192661</v>
+        <v>458.1834862385321</v>
       </c>
       <c r="G38" t="n">
-        <v>54.23340877145928</v>
+        <v>108.4668175429186</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>148.327</v>
+        <v>296.654</v>
       </c>
       <c r="D39" t="n">
         <v>658</v>
       </c>
       <c r="E39" t="n">
-        <v>224</v>
+        <v>448</v>
       </c>
       <c r="F39" t="n">
-        <v>225.0668693009119</v>
+        <v>450.1337386018237</v>
       </c>
       <c r="G39" t="n">
-        <v>27.34833806193742</v>
+        <v>54.69667612387484</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1620,19 +1620,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>150.122</v>
+        <v>300.244</v>
       </c>
       <c r="D40" t="n">
         <v>692</v>
       </c>
       <c r="E40" t="n">
-        <v>215.5</v>
+        <v>431</v>
       </c>
       <c r="F40" t="n">
-        <v>216.3959537572254</v>
+        <v>432.7919075144509</v>
       </c>
       <c r="G40" t="n">
-        <v>16.69230819641347</v>
+        <v>33.38461639282695</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>150.167</v>
+        <v>300.334</v>
       </c>
       <c r="D41" t="n">
         <v>703</v>
       </c>
       <c r="E41" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F41" t="n">
-        <v>213.3926031294452</v>
+        <v>426.7852062588905</v>
       </c>
       <c r="G41" t="n">
-        <v>16.7658434461833</v>
+        <v>33.5316868923666</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1680,19 +1680,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>149.942</v>
+        <v>299.884</v>
       </c>
       <c r="D42" t="n">
         <v>641</v>
       </c>
       <c r="E42" t="n">
-        <v>231</v>
+        <v>462</v>
       </c>
       <c r="F42" t="n">
-        <v>233.4555382215289</v>
+        <v>466.9110764430577</v>
       </c>
       <c r="G42" t="n">
-        <v>16.44122974982186</v>
+        <v>32.88245949964372</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1710,19 +1710,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>149.936</v>
+        <v>299.872</v>
       </c>
       <c r="D43" t="n">
         <v>676</v>
       </c>
       <c r="E43" t="n">
-        <v>222</v>
+        <v>444</v>
       </c>
       <c r="F43" t="n">
-        <v>221.4733727810651</v>
+        <v>442.9467455621302</v>
       </c>
       <c r="G43" t="n">
-        <v>12.99279120413169</v>
+        <v>25.98558240826338</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>149.964</v>
+        <v>299.928</v>
       </c>
       <c r="D44" t="n">
         <v>625</v>
       </c>
       <c r="E44" t="n">
-        <v>239</v>
+        <v>478</v>
       </c>
       <c r="F44" t="n">
-        <v>239.5088</v>
+        <v>479.0176</v>
       </c>
       <c r="G44" t="n">
-        <v>15.04321774089573</v>
+        <v>30.08643548179145</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1770,19 +1770,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>149.984</v>
+        <v>299.968</v>
       </c>
       <c r="D45" t="n">
         <v>644</v>
       </c>
       <c r="E45" t="n">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="F45" t="n">
-        <v>232.6506211180124</v>
+        <v>465.3012422360248</v>
       </c>
       <c r="G45" t="n">
-        <v>18.28495671078614</v>
+        <v>36.56991342157228</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>149.658</v>
+        <v>299.316</v>
       </c>
       <c r="D46" t="n">
         <v>675</v>
       </c>
       <c r="E46" t="n">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="F46" t="n">
-        <v>221.3407407407407</v>
+        <v>442.6814814814815</v>
       </c>
       <c r="G46" t="n">
-        <v>18.87533793710212</v>
+        <v>37.75067587420425</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1830,19 +1830,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>150.114</v>
+        <v>300.228</v>
       </c>
       <c r="D47" t="n">
         <v>684</v>
       </c>
       <c r="E47" t="n">
-        <v>219</v>
+        <v>438</v>
       </c>
       <c r="F47" t="n">
-        <v>219.0570175438596</v>
+        <v>438.1140350877193</v>
       </c>
       <c r="G47" t="n">
-        <v>14.63838274415107</v>
+        <v>29.27676548830215</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>150.097</v>
+        <v>300.194</v>
       </c>
       <c r="D48" t="n">
         <v>629</v>
       </c>
       <c r="E48" t="n">
-        <v>238</v>
+        <v>476</v>
       </c>
       <c r="F48" t="n">
-        <v>238.060413354531</v>
+        <v>476.120826709062</v>
       </c>
       <c r="G48" t="n">
-        <v>21.28056828313261</v>
+        <v>42.56113656626523</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1890,19 +1890,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>150.096</v>
+        <v>300.192</v>
       </c>
       <c r="D49" t="n">
         <v>636</v>
       </c>
       <c r="E49" t="n">
-        <v>235</v>
+        <v>470</v>
       </c>
       <c r="F49" t="n">
-        <v>235.5298742138365</v>
+        <v>471.059748427673</v>
       </c>
       <c r="G49" t="n">
-        <v>18.52848126363596</v>
+        <v>37.05696252727192</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1920,19 +1920,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>150.072</v>
+        <v>300.144</v>
       </c>
       <c r="D50" t="n">
         <v>632</v>
       </c>
       <c r="E50" t="n">
-        <v>233.5</v>
+        <v>467</v>
       </c>
       <c r="F50" t="n">
-        <v>236.9541139240506</v>
+        <v>473.9082278481013</v>
       </c>
       <c r="G50" t="n">
-        <v>24.74771818080553</v>
+        <v>49.49543636161107</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1950,19 +1950,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>150.098</v>
+        <v>300.196</v>
       </c>
       <c r="D51" t="n">
         <v>612</v>
       </c>
       <c r="E51" t="n">
-        <v>243</v>
+        <v>486</v>
       </c>
       <c r="F51" t="n">
-        <v>245.0098039215686</v>
+        <v>490.0196078431372</v>
       </c>
       <c r="G51" t="n">
-        <v>24.87395199830263</v>
+        <v>49.74790399660526</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1980,19 +1980,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>150.043</v>
+        <v>300.086</v>
       </c>
       <c r="D52" t="n">
         <v>697</v>
       </c>
       <c r="E52" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F52" t="n">
-        <v>214.8292682926829</v>
+        <v>429.6585365853659</v>
       </c>
       <c r="G52" t="n">
-        <v>15.64249861198345</v>
+        <v>31.2849972239669</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2010,19 +2010,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>150.076</v>
+        <v>300.152</v>
       </c>
       <c r="D53" t="n">
         <v>683</v>
       </c>
       <c r="E53" t="n">
-        <v>217</v>
+        <v>434</v>
       </c>
       <c r="F53" t="n">
-        <v>219.3191800878477</v>
+        <v>438.6383601756955</v>
       </c>
       <c r="G53" t="n">
-        <v>20.66477369956011</v>
+        <v>41.32954739912022</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2040,19 +2040,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>150.398</v>
+        <v>300.796</v>
       </c>
       <c r="D54" t="n">
         <v>715</v>
       </c>
       <c r="E54" t="n">
-        <v>209</v>
+        <v>418</v>
       </c>
       <c r="F54" t="n">
-        <v>209.9706293706294</v>
+        <v>419.9412587412588</v>
       </c>
       <c r="G54" t="n">
-        <v>12.55901381616846</v>
+        <v>25.11802763233693</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2070,19 +2070,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>149.895</v>
+        <v>299.79</v>
       </c>
       <c r="D55" t="n">
         <v>761</v>
       </c>
       <c r="E55" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="F55" t="n">
-        <v>196.6504599211564</v>
+        <v>393.3009198423127</v>
       </c>
       <c r="G55" t="n">
-        <v>20.61760305441074</v>
+        <v>41.23520610882147</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2100,19 +2100,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>150.333</v>
+        <v>300.666</v>
       </c>
       <c r="D56" t="n">
         <v>691</v>
       </c>
       <c r="E56" t="n">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="F56" t="n">
-        <v>217.2373371924747</v>
+        <v>434.4746743849494</v>
       </c>
       <c r="G56" t="n">
-        <v>27.81411060669043</v>
+        <v>55.62822121338085</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>149.964</v>
+        <v>299.928</v>
       </c>
       <c r="D57" t="n">
         <v>713</v>
       </c>
       <c r="E57" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="F57" t="n">
-        <v>209.9228611500701</v>
+        <v>419.8457223001403</v>
       </c>
       <c r="G57" t="n">
-        <v>23.25405478002568</v>
+        <v>46.50810956005136</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2160,19 +2160,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>150.089</v>
+        <v>300.178</v>
       </c>
       <c r="D58" t="n">
         <v>661</v>
       </c>
       <c r="E58" t="n">
-        <v>214</v>
+        <v>428</v>
       </c>
       <c r="F58" t="n">
-        <v>226.5763993948563</v>
+        <v>453.1527987897126</v>
       </c>
       <c r="G58" t="n">
-        <v>51.68842247471953</v>
+        <v>103.3768449494391</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2190,19 +2190,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>150.138</v>
+        <v>300.276</v>
       </c>
       <c r="D59" t="n">
         <v>704</v>
       </c>
       <c r="E59" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F59" t="n">
-        <v>212.7897727272727</v>
+        <v>425.5795454545454</v>
       </c>
       <c r="G59" t="n">
-        <v>11.97228225862886</v>
+        <v>23.94456451725772</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>149.816</v>
+        <v>299.632</v>
       </c>
       <c r="D60" t="n">
         <v>694</v>
       </c>
       <c r="E60" t="n">
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="F60" t="n">
-        <v>215.3876080691643</v>
+        <v>430.7752161383285</v>
       </c>
       <c r="G60" t="n">
-        <v>14.95103761857827</v>
+        <v>29.90207523715654</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>150.029</v>
+        <v>300.058</v>
       </c>
       <c r="D61" t="n">
         <v>722</v>
       </c>
       <c r="E61" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="F61" t="n">
-        <v>207.4930747922438</v>
+        <v>414.9861495844875</v>
       </c>
       <c r="G61" t="n">
-        <v>12.76135731273095</v>
+        <v>25.5227146254619</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2280,19 +2280,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>53.118</v>
+        <v>106.236</v>
       </c>
       <c r="D62" t="n">
         <v>176</v>
       </c>
       <c r="E62" t="n">
-        <v>245</v>
+        <v>490</v>
       </c>
       <c r="F62" t="n">
-        <v>246.9147727272727</v>
+        <v>493.8295454545454</v>
       </c>
       <c r="G62" t="n">
-        <v>15.43793501937152</v>
+        <v>30.87587003874305</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2310,19 +2310,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>136.298</v>
+        <v>272.596</v>
       </c>
       <c r="D63" t="n">
         <v>602</v>
       </c>
       <c r="E63" t="n">
-        <v>223.5</v>
+        <v>447</v>
       </c>
       <c r="F63" t="n">
-        <v>226.0448504983389</v>
+        <v>452.0897009966777</v>
       </c>
       <c r="G63" t="n">
-        <v>20.06743162541834</v>
+        <v>40.13486325083667</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2340,19 +2340,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>150.106</v>
+        <v>300.212</v>
       </c>
       <c r="D64" t="n">
         <v>585</v>
       </c>
       <c r="E64" t="n">
-        <v>257</v>
+        <v>514</v>
       </c>
       <c r="F64" t="n">
-        <v>256.2837606837607</v>
+        <v>512.5675213675214</v>
       </c>
       <c r="G64" t="n">
-        <v>18.78149846160251</v>
+        <v>37.56299692320503</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2370,19 +2370,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>150.165</v>
+        <v>300.33</v>
       </c>
       <c r="D65" t="n">
         <v>681</v>
       </c>
       <c r="E65" t="n">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="F65" t="n">
-        <v>220.2055800293686</v>
+        <v>440.4111600587372</v>
       </c>
       <c r="G65" t="n">
-        <v>11.15487355874555</v>
+        <v>22.3097471174911</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2400,19 +2400,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>71.60299999999999</v>
+        <v>143.206</v>
       </c>
       <c r="D66" t="n">
         <v>321</v>
       </c>
       <c r="E66" t="n">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="F66" t="n">
-        <v>221.9190031152648</v>
+        <v>443.8380062305296</v>
       </c>
       <c r="G66" t="n">
-        <v>33.20541626004883</v>
+        <v>66.41083252009766</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2430,19 +2430,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>59.893</v>
+        <v>119.786</v>
       </c>
       <c r="D67" t="n">
         <v>156</v>
       </c>
       <c r="E67" t="n">
-        <v>356.5</v>
+        <v>713</v>
       </c>
       <c r="F67" t="n">
-        <v>372.7179487179487</v>
+        <v>745.4358974358975</v>
       </c>
       <c r="G67" t="n">
-        <v>129.3687300738721</v>
+        <v>258.7374601477442</v>
       </c>
       <c r="H67" t="n">
         <v>13</v>
@@ -2460,19 +2460,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>85.908</v>
+        <v>171.816</v>
       </c>
       <c r="D68" t="n">
         <v>387</v>
       </c>
       <c r="E68" t="n">
-        <v>218</v>
+        <v>436</v>
       </c>
       <c r="F68" t="n">
-        <v>221.3333333333333</v>
+        <v>442.6666666666667</v>
       </c>
       <c r="G68" t="n">
-        <v>27.46670146048067</v>
+        <v>54.93340292096134</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2490,19 +2490,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>110.12</v>
+        <v>220.24</v>
       </c>
       <c r="D69" t="n">
         <v>450</v>
       </c>
       <c r="E69" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="F69" t="n">
-        <v>244.0333333333333</v>
+        <v>488.0666666666667</v>
       </c>
       <c r="G69" t="n">
-        <v>28.1006978648214</v>
+        <v>56.20139572964279</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2520,19 +2520,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>150.101</v>
+        <v>300.202</v>
       </c>
       <c r="D70" t="n">
         <v>676</v>
       </c>
       <c r="E70" t="n">
-        <v>221</v>
+        <v>442</v>
       </c>
       <c r="F70" t="n">
-        <v>221.7840236686391</v>
+        <v>443.5680473372781</v>
       </c>
       <c r="G70" t="n">
-        <v>8.386273392618158</v>
+        <v>16.77254678523632</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>103.805</v>
+        <v>207.61</v>
       </c>
       <c r="D71" t="n">
         <v>469</v>
       </c>
       <c r="E71" t="n">
-        <v>222</v>
+        <v>444</v>
       </c>
       <c r="F71" t="n">
-        <v>220.5522388059701</v>
+        <v>441.1044776119403</v>
       </c>
       <c r="G71" t="n">
-        <v>19.93161225253955</v>
+        <v>39.86322450507911</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2580,19 +2580,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>150.466</v>
+        <v>300.932</v>
       </c>
       <c r="D72" t="n">
         <v>676</v>
       </c>
       <c r="E72" t="n">
-        <v>221</v>
+        <v>442</v>
       </c>
       <c r="F72" t="n">
-        <v>222.1804733727811</v>
+        <v>444.3609467455621</v>
       </c>
       <c r="G72" t="n">
-        <v>20.4375102581837</v>
+        <v>40.8750205163674</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2610,19 +2610,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>104.071</v>
+        <v>208.142</v>
       </c>
       <c r="D73" t="n">
         <v>465</v>
       </c>
       <c r="E73" t="n">
-        <v>223</v>
+        <v>446</v>
       </c>
       <c r="F73" t="n">
-        <v>223.3225806451613</v>
+        <v>446.6451612903226</v>
       </c>
       <c r="G73" t="n">
-        <v>17.03960984502712</v>
+        <v>34.07921969005425</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2640,19 +2640,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>149.992</v>
+        <v>299.984</v>
       </c>
       <c r="D74" t="n">
         <v>658</v>
       </c>
       <c r="E74" t="n">
-        <v>226</v>
+        <v>452</v>
       </c>
       <c r="F74" t="n">
-        <v>227.6884498480243</v>
+        <v>455.3768996960486</v>
       </c>
       <c r="G74" t="n">
-        <v>20.62018385146595</v>
+        <v>41.2403677029319</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2670,19 +2670,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>161.203</v>
+        <v>322.406</v>
       </c>
       <c r="D75" t="n">
         <v>673</v>
       </c>
       <c r="E75" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F75" t="n">
-        <v>239.2184249628529</v>
+        <v>478.4368499257058</v>
       </c>
       <c r="G75" t="n">
-        <v>23.47639681967005</v>
+        <v>46.9527936393401</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2751,19 +2751,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123.55</v>
+        <v>247.1</v>
       </c>
       <c r="D2" t="n">
         <v>377</v>
       </c>
       <c r="E2" t="n">
-        <v>327</v>
+        <v>654</v>
       </c>
       <c r="F2" t="n">
-        <v>326.816976127321</v>
+        <v>653.6339522546419</v>
       </c>
       <c r="G2" t="n">
-        <v>24.0414298522886</v>
+        <v>48.08285970457721</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>150.073</v>
+        <v>300.146</v>
       </c>
       <c r="D3" t="n">
         <v>264</v>
       </c>
       <c r="E3" t="n">
-        <v>404.5</v>
+        <v>809</v>
       </c>
       <c r="F3" t="n">
-        <v>419.9962121212121</v>
+        <v>839.9924242424242</v>
       </c>
       <c r="G3" t="n">
-        <v>80.68713921230955</v>
+        <v>161.3742784246191</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -2811,19 +2811,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>132.415</v>
+        <v>264.83</v>
       </c>
       <c r="D4" t="n">
         <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>263</v>
+        <v>526</v>
       </c>
       <c r="F4" t="n">
-        <v>264.37</v>
+        <v>528.74</v>
       </c>
       <c r="G4" t="n">
-        <v>15.77068575104191</v>
+        <v>31.54137150208381</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>149.87</v>
+        <v>299.74</v>
       </c>
       <c r="D5" t="n">
         <v>433</v>
       </c>
       <c r="E5" t="n">
-        <v>345</v>
+        <v>690</v>
       </c>
       <c r="F5" t="n">
-        <v>345.2886836027714</v>
+        <v>690.5773672055427</v>
       </c>
       <c r="G5" t="n">
-        <v>36.26321325436572</v>
+        <v>72.52642650873145</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2871,19 +2871,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>149.982</v>
+        <v>299.964</v>
       </c>
       <c r="D6" t="n">
         <v>365</v>
       </c>
       <c r="E6" t="n">
-        <v>416</v>
+        <v>832</v>
       </c>
       <c r="F6" t="n">
-        <v>410.2821917808219</v>
+        <v>820.5643835616438</v>
       </c>
       <c r="G6" t="n">
-        <v>36.20249574932097</v>
+        <v>72.40499149864193</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2901,19 +2901,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>126.438</v>
+        <v>252.876</v>
       </c>
       <c r="D7" t="n">
         <v>329</v>
       </c>
       <c r="E7" t="n">
-        <v>384</v>
+        <v>768</v>
       </c>
       <c r="F7" t="n">
-        <v>383.2948328267477</v>
+        <v>766.5896656534954</v>
       </c>
       <c r="G7" t="n">
-        <v>38.88986956684525</v>
+        <v>77.7797391336905</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2931,19 +2931,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.548</v>
+        <v>183.096</v>
       </c>
       <c r="D8" t="n">
         <v>444</v>
       </c>
       <c r="E8" t="n">
-        <v>201</v>
+        <v>402</v>
       </c>
       <c r="F8" t="n">
-        <v>205.6396396396396</v>
+        <v>411.2792792792793</v>
       </c>
       <c r="G8" t="n">
-        <v>21.92869330210004</v>
+        <v>43.85738660420009</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2961,19 +2961,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150.34</v>
+        <v>300.68</v>
       </c>
       <c r="D9" t="n">
         <v>384</v>
       </c>
       <c r="E9" t="n">
-        <v>390.5</v>
+        <v>781</v>
       </c>
       <c r="F9" t="n">
-        <v>391.0208333333333</v>
+        <v>782.0416666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>38.26449906373767</v>
+        <v>76.52899812747535</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -2991,19 +2991,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149.957</v>
+        <v>299.914</v>
       </c>
       <c r="D10" t="n">
         <v>426</v>
       </c>
       <c r="E10" t="n">
-        <v>351.5</v>
+        <v>703</v>
       </c>
       <c r="F10" t="n">
-        <v>351.2582159624413</v>
+        <v>702.5164319248827</v>
       </c>
       <c r="G10" t="n">
-        <v>31.15568482709079</v>
+        <v>62.31136965418158</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -3021,19 +3021,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>89.393</v>
+        <v>178.786</v>
       </c>
       <c r="D11" t="n">
         <v>249</v>
       </c>
       <c r="E11" t="n">
-        <v>357</v>
+        <v>714</v>
       </c>
       <c r="F11" t="n">
-        <v>357.6265060240964</v>
+        <v>715.2530120481928</v>
       </c>
       <c r="G11" t="n">
-        <v>35.08711882587357</v>
+        <v>70.17423765174715</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3051,19 +3051,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.707</v>
+        <v>299.414</v>
       </c>
       <c r="D12" t="n">
         <v>460</v>
       </c>
       <c r="E12" t="n">
-        <v>304</v>
+        <v>608</v>
       </c>
       <c r="F12" t="n">
-        <v>324.6195652173913</v>
+        <v>649.2391304347826</v>
       </c>
       <c r="G12" t="n">
-        <v>79.8954712521801</v>
+        <v>159.7909425043602</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3081,19 +3081,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>150.176</v>
+        <v>300.352</v>
       </c>
       <c r="D13" t="n">
         <v>506</v>
       </c>
       <c r="E13" t="n">
-        <v>290</v>
+        <v>580</v>
       </c>
       <c r="F13" t="n">
-        <v>296.0849802371541</v>
+        <v>592.1699604743083</v>
       </c>
       <c r="G13" t="n">
-        <v>30.07592194581403</v>
+        <v>60.15184389162805</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -3111,19 +3111,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>149.498</v>
+        <v>298.996</v>
       </c>
       <c r="D14" t="n">
         <v>332</v>
       </c>
       <c r="E14" t="n">
-        <v>484.5</v>
+        <v>969</v>
       </c>
       <c r="F14" t="n">
-        <v>448.9036144578313</v>
+        <v>897.8072289156627</v>
       </c>
       <c r="G14" t="n">
-        <v>140.880345146254</v>
+        <v>281.7606902925079</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>98.601</v>
+        <v>197.202</v>
       </c>
       <c r="D15" t="n">
         <v>261</v>
       </c>
       <c r="E15" t="n">
-        <v>368</v>
+        <v>736</v>
       </c>
       <c r="F15" t="n">
-        <v>374.3409961685824</v>
+        <v>748.6819923371647</v>
       </c>
       <c r="G15" t="n">
-        <v>88.05218407593472</v>
+        <v>176.1043681518694</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -3171,19 +3171,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>149.708</v>
+        <v>299.416</v>
       </c>
       <c r="D16" t="n">
         <v>384</v>
       </c>
       <c r="E16" t="n">
-        <v>394</v>
+        <v>788</v>
       </c>
       <c r="F16" t="n">
-        <v>389.0182291666667</v>
+        <v>778.0364583333334</v>
       </c>
       <c r="G16" t="n">
-        <v>28.76486435565172</v>
+        <v>57.52972871130343</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3201,19 +3201,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>149.995</v>
+        <v>299.99</v>
       </c>
       <c r="D17" t="n">
         <v>330</v>
       </c>
       <c r="E17" t="n">
-        <v>464.5</v>
+        <v>929</v>
       </c>
       <c r="F17" t="n">
-        <v>452.8242424242424</v>
+        <v>905.6484848484848</v>
       </c>
       <c r="G17" t="n">
-        <v>114.6876795833298</v>
+        <v>229.3753591666596</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3231,19 +3231,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>75.01000000000001</v>
+        <v>150.02</v>
       </c>
       <c r="D18" t="n">
         <v>369</v>
       </c>
       <c r="E18" t="n">
-        <v>179</v>
+        <v>358</v>
       </c>
       <c r="F18" t="n">
-        <v>202.7642276422764</v>
+        <v>405.5284552845528</v>
       </c>
       <c r="G18" t="n">
-        <v>53.91061663926966</v>
+        <v>107.8212332785393</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>149.99</v>
+        <v>299.98</v>
       </c>
       <c r="D19" t="n">
         <v>312</v>
       </c>
       <c r="E19" t="n">
-        <v>447.5</v>
+        <v>895</v>
       </c>
       <c r="F19" t="n">
-        <v>477.7948717948718</v>
+        <v>955.5897435897435</v>
       </c>
       <c r="G19" t="n">
-        <v>148.426677815827</v>
+        <v>296.853355631654</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>150.046</v>
+        <v>300.092</v>
       </c>
       <c r="D20" t="n">
         <v>379</v>
       </c>
       <c r="E20" t="n">
-        <v>392</v>
+        <v>784</v>
       </c>
       <c r="F20" t="n">
-        <v>395.4643799472295</v>
+        <v>790.9287598944591</v>
       </c>
       <c r="G20" t="n">
-        <v>46.24853119730581</v>
+        <v>92.49706239461162</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -3321,19 +3321,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>149.776</v>
+        <v>299.552</v>
       </c>
       <c r="D21" t="n">
         <v>335</v>
       </c>
       <c r="E21" t="n">
-        <v>460</v>
+        <v>920</v>
       </c>
       <c r="F21" t="n">
-        <v>445.8626865671642</v>
+        <v>891.7253731343284</v>
       </c>
       <c r="G21" t="n">
-        <v>103.3312457973396</v>
+        <v>206.6624915946792</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -3351,19 +3351,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>150.094</v>
+        <v>300.188</v>
       </c>
       <c r="D22" t="n">
         <v>382</v>
       </c>
       <c r="E22" t="n">
-        <v>395.5</v>
+        <v>791</v>
       </c>
       <c r="F22" t="n">
-        <v>392.3429319371728</v>
+        <v>784.6858638743455</v>
       </c>
       <c r="G22" t="n">
-        <v>77.74033222448504</v>
+        <v>155.4806644489701</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -3381,19 +3381,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D23" t="n">
         <v>397</v>
       </c>
       <c r="E23" t="n">
-        <v>376</v>
+        <v>752</v>
       </c>
       <c r="F23" t="n">
-        <v>376.9823677581864</v>
+        <v>753.9647355163728</v>
       </c>
       <c r="G23" t="n">
-        <v>95.96612508102237</v>
+        <v>191.9322501620447</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3411,19 +3411,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>149.823</v>
+        <v>299.646</v>
       </c>
       <c r="D24" t="n">
         <v>416</v>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>706</v>
       </c>
       <c r="F24" t="n">
-        <v>359.3028846153846</v>
+        <v>718.6057692307693</v>
       </c>
       <c r="G24" t="n">
-        <v>50.093787618067</v>
+        <v>100.187575236134</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -3441,19 +3441,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>103.941</v>
+        <v>207.882</v>
       </c>
       <c r="D25" t="n">
         <v>314</v>
       </c>
       <c r="E25" t="n">
-        <v>328</v>
+        <v>656</v>
       </c>
       <c r="F25" t="n">
-        <v>329.6815286624204</v>
+        <v>659.3630573248407</v>
       </c>
       <c r="G25" t="n">
-        <v>22.70284164464853</v>
+        <v>45.40568328929705</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -3471,19 +3471,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>149.98</v>
+        <v>299.96</v>
       </c>
       <c r="D26" t="n">
         <v>389</v>
       </c>
       <c r="E26" t="n">
-        <v>383</v>
+        <v>766</v>
       </c>
       <c r="F26" t="n">
-        <v>384.3341902313625</v>
+        <v>768.6683804627249</v>
       </c>
       <c r="G26" t="n">
-        <v>47.30741085527402</v>
+        <v>94.61482171054804</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3501,19 +3501,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>149.955</v>
+        <v>299.91</v>
       </c>
       <c r="D27" t="n">
         <v>372</v>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>784</v>
       </c>
       <c r="F27" t="n">
-        <v>402.3306451612903</v>
+        <v>804.6612903225806</v>
       </c>
       <c r="G27" t="n">
-        <v>89.92857798945387</v>
+        <v>179.8571559789077</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3531,19 +3531,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>149.701</v>
+        <v>299.402</v>
       </c>
       <c r="D28" t="n">
         <v>310</v>
       </c>
       <c r="E28" t="n">
-        <v>498</v>
+        <v>996</v>
       </c>
       <c r="F28" t="n">
-        <v>481.8806451612903</v>
+        <v>963.7612903225806</v>
       </c>
       <c r="G28" t="n">
-        <v>62.57124312015734</v>
+        <v>125.1424862403147</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3561,19 +3561,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>112.309</v>
+        <v>224.618</v>
       </c>
       <c r="D29" t="n">
         <v>352</v>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>616</v>
       </c>
       <c r="F29" t="n">
-        <v>318.2130681818182</v>
+        <v>636.4261363636364</v>
       </c>
       <c r="G29" t="n">
-        <v>42.78772289390358</v>
+        <v>85.57544578780715</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>149.78</v>
+        <v>299.56</v>
       </c>
       <c r="D30" t="n">
         <v>419</v>
       </c>
       <c r="E30" t="n">
-        <v>354</v>
+        <v>708</v>
       </c>
       <c r="F30" t="n">
-        <v>356.7064439140811</v>
+        <v>713.4128878281623</v>
       </c>
       <c r="G30" t="n">
-        <v>43.49874585997837</v>
+        <v>86.99749171995674</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3621,19 +3621,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>147.216</v>
+        <v>294.432</v>
       </c>
       <c r="D31" t="n">
         <v>355</v>
       </c>
       <c r="E31" t="n">
-        <v>439</v>
+        <v>878</v>
       </c>
       <c r="F31" t="n">
-        <v>413.6647887323944</v>
+        <v>827.3295774647887</v>
       </c>
       <c r="G31" t="n">
-        <v>106.9131744174164</v>
+        <v>213.8263488348329</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>145.785</v>
+        <v>291.57</v>
       </c>
       <c r="D32" t="n">
         <v>435</v>
       </c>
       <c r="E32" t="n">
-        <v>328</v>
+        <v>656</v>
       </c>
       <c r="F32" t="n">
-        <v>334.4919540229885</v>
+        <v>668.983908045977</v>
       </c>
       <c r="G32" t="n">
-        <v>51.57055749699509</v>
+        <v>103.1411149939902</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3681,19 +3681,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>149.777</v>
+        <v>299.554</v>
       </c>
       <c r="D33" t="n">
         <v>394</v>
       </c>
       <c r="E33" t="n">
-        <v>373</v>
+        <v>746</v>
       </c>
       <c r="F33" t="n">
-        <v>378.9340101522843</v>
+        <v>757.8680203045685</v>
       </c>
       <c r="G33" t="n">
-        <v>50.97443065718659</v>
+        <v>101.9488613143732</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3711,19 +3711,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>149.889</v>
+        <v>299.778</v>
       </c>
       <c r="D34" t="n">
         <v>450</v>
       </c>
       <c r="E34" t="n">
-        <v>327</v>
+        <v>654</v>
       </c>
       <c r="F34" t="n">
-        <v>332.2511111111111</v>
+        <v>664.5022222222223</v>
       </c>
       <c r="G34" t="n">
-        <v>30.23503419461138</v>
+        <v>60.47006838922276</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -3741,19 +3741,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>150.073</v>
+        <v>300.146</v>
       </c>
       <c r="D35" t="n">
         <v>426</v>
       </c>
       <c r="E35" t="n">
-        <v>348</v>
+        <v>696</v>
       </c>
       <c r="F35" t="n">
-        <v>351.5352112676056</v>
+        <v>703.0704225352113</v>
       </c>
       <c r="G35" t="n">
-        <v>26.97798544046329</v>
+        <v>53.95597088092658</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>150.102</v>
+        <v>300.204</v>
       </c>
       <c r="D36" t="n">
         <v>340</v>
       </c>
       <c r="E36" t="n">
-        <v>444</v>
+        <v>888</v>
       </c>
       <c r="F36" t="n">
-        <v>440.8735294117647</v>
+        <v>881.7470588235294</v>
       </c>
       <c r="G36" t="n">
-        <v>42.62180400096959</v>
+        <v>85.24360800193918</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3801,19 +3801,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>150.159</v>
+        <v>300.318</v>
       </c>
       <c r="D37" t="n">
         <v>451</v>
       </c>
       <c r="E37" t="n">
-        <v>330</v>
+        <v>660</v>
       </c>
       <c r="F37" t="n">
-        <v>331.9578713968958</v>
+        <v>663.9157427937915</v>
       </c>
       <c r="G37" t="n">
-        <v>19.06819338622659</v>
+        <v>38.13638677245319</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>149.893</v>
+        <v>299.786</v>
       </c>
       <c r="D38" t="n">
         <v>322</v>
       </c>
       <c r="E38" t="n">
-        <v>452.5</v>
+        <v>905</v>
       </c>
       <c r="F38" t="n">
-        <v>464.3664596273292</v>
+        <v>928.7329192546584</v>
       </c>
       <c r="G38" t="n">
-        <v>150.8033395533684</v>
+        <v>301.6066791067367</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>148.993</v>
+        <v>297.986</v>
       </c>
       <c r="D39" t="n">
         <v>413</v>
       </c>
       <c r="E39" t="n">
-        <v>347</v>
+        <v>694</v>
       </c>
       <c r="F39" t="n">
-        <v>359.861985472155</v>
+        <v>719.7239709443099</v>
       </c>
       <c r="G39" t="n">
-        <v>76.2484304019878</v>
+        <v>152.4968608039756</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3891,19 +3891,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>149.91</v>
+        <v>299.82</v>
       </c>
       <c r="D40" t="n">
         <v>383</v>
       </c>
       <c r="E40" t="n">
-        <v>392</v>
+        <v>784</v>
       </c>
       <c r="F40" t="n">
-        <v>390.5483028720627</v>
+        <v>781.0966057441253</v>
       </c>
       <c r="G40" t="n">
-        <v>42.4935737795404</v>
+        <v>84.9871475590808</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3921,19 +3921,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>150.129</v>
+        <v>300.258</v>
       </c>
       <c r="D41" t="n">
         <v>522</v>
       </c>
       <c r="E41" t="n">
-        <v>273</v>
+        <v>546</v>
       </c>
       <c r="F41" t="n">
-        <v>286.9003831417625</v>
+        <v>573.8007662835249</v>
       </c>
       <c r="G41" t="n">
-        <v>65.86723720115479</v>
+        <v>131.7344744023096</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3951,19 +3951,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>149.876</v>
+        <v>299.752</v>
       </c>
       <c r="D42" t="n">
         <v>412</v>
       </c>
       <c r="E42" t="n">
-        <v>357</v>
+        <v>714</v>
       </c>
       <c r="F42" t="n">
-        <v>362.9150485436893</v>
+        <v>725.8300970873786</v>
       </c>
       <c r="G42" t="n">
-        <v>54.58474129494505</v>
+        <v>109.1694825898901</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>150.113</v>
+        <v>300.226</v>
       </c>
       <c r="D43" t="n">
         <v>415</v>
       </c>
       <c r="E43" t="n">
-        <v>349</v>
+        <v>698</v>
       </c>
       <c r="F43" t="n">
-        <v>361.1156626506024</v>
+        <v>722.2313253012048</v>
       </c>
       <c r="G43" t="n">
-        <v>70.72865151685819</v>
+        <v>141.4573030337164</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -4011,19 +4011,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>149.876</v>
+        <v>299.752</v>
       </c>
       <c r="D44" t="n">
         <v>442</v>
       </c>
       <c r="E44" t="n">
-        <v>337</v>
+        <v>674</v>
       </c>
       <c r="F44" t="n">
-        <v>338.2013574660634</v>
+        <v>676.4027149321267</v>
       </c>
       <c r="G44" t="n">
-        <v>21.74960990530465</v>
+        <v>43.4992198106093</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4041,19 +4041,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>150.299</v>
+        <v>300.598</v>
       </c>
       <c r="D45" t="n">
         <v>394</v>
       </c>
       <c r="E45" t="n">
-        <v>387</v>
+        <v>774</v>
       </c>
       <c r="F45" t="n">
-        <v>380.3604060913706</v>
+        <v>760.7208121827412</v>
       </c>
       <c r="G45" t="n">
-        <v>76.22043200681433</v>
+        <v>152.4408640136287</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -4071,19 +4071,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>149.665</v>
+        <v>299.33</v>
       </c>
       <c r="D46" t="n">
         <v>392</v>
       </c>
       <c r="E46" t="n">
-        <v>384.5</v>
+        <v>769</v>
       </c>
       <c r="F46" t="n">
-        <v>380.7040816326531</v>
+        <v>761.4081632653061</v>
       </c>
       <c r="G46" t="n">
-        <v>47.11485866020745</v>
+        <v>94.22971732041489</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -4101,19 +4101,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>149.372</v>
+        <v>298.744</v>
       </c>
       <c r="D47" t="n">
         <v>370</v>
       </c>
       <c r="E47" t="n">
-        <v>404</v>
+        <v>808</v>
       </c>
       <c r="F47" t="n">
-        <v>402.4756756756757</v>
+        <v>804.9513513513514</v>
       </c>
       <c r="G47" t="n">
-        <v>28.51007909452076</v>
+        <v>57.02015818904152</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -4131,19 +4131,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>150.145</v>
+        <v>300.29</v>
       </c>
       <c r="D48" t="n">
         <v>391</v>
       </c>
       <c r="E48" t="n">
-        <v>386</v>
+        <v>772</v>
       </c>
       <c r="F48" t="n">
-        <v>383.1304347826087</v>
+        <v>766.2608695652174</v>
       </c>
       <c r="G48" t="n">
-        <v>24.85116454094755</v>
+        <v>49.70232908189509</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>150.137</v>
+        <v>300.274</v>
       </c>
       <c r="D49" t="n">
         <v>420</v>
       </c>
       <c r="E49" t="n">
-        <v>358</v>
+        <v>716</v>
       </c>
       <c r="F49" t="n">
-        <v>357.0047619047619</v>
+        <v>714.0095238095238</v>
       </c>
       <c r="G49" t="n">
-        <v>27.77578100941596</v>
+        <v>55.55156201883192</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -4191,19 +4191,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>149.851</v>
+        <v>299.702</v>
       </c>
       <c r="D50" t="n">
         <v>417</v>
       </c>
       <c r="E50" t="n">
-        <v>359</v>
+        <v>718</v>
       </c>
       <c r="F50" t="n">
-        <v>358.9280575539568</v>
+        <v>717.8561151079136</v>
       </c>
       <c r="G50" t="n">
-        <v>16.32437430525954</v>
+        <v>32.64874861051909</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>150.037</v>
+        <v>300.074</v>
       </c>
       <c r="D51" t="n">
         <v>467</v>
       </c>
       <c r="E51" t="n">
-        <v>316</v>
+        <v>632</v>
       </c>
       <c r="F51" t="n">
-        <v>320.4625267665953</v>
+        <v>640.9250535331906</v>
       </c>
       <c r="G51" t="n">
-        <v>33.29340544255371</v>
+        <v>66.58681088510741</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -4251,19 +4251,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>150.124</v>
+        <v>300.248</v>
       </c>
       <c r="D52" t="n">
         <v>444</v>
       </c>
       <c r="E52" t="n">
-        <v>338</v>
+        <v>676</v>
       </c>
       <c r="F52" t="n">
-        <v>337.5382882882883</v>
+        <v>675.0765765765766</v>
       </c>
       <c r="G52" t="n">
-        <v>38.85623060859836</v>
+        <v>77.71246121719672</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -4281,19 +4281,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>150.148</v>
+        <v>300.296</v>
       </c>
       <c r="D53" t="n">
         <v>426</v>
       </c>
       <c r="E53" t="n">
-        <v>348.5</v>
+        <v>697</v>
       </c>
       <c r="F53" t="n">
-        <v>351.6924882629108</v>
+        <v>703.3849765258216</v>
       </c>
       <c r="G53" t="n">
-        <v>30.71718108859069</v>
+        <v>61.43436217718138</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -4311,19 +4311,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>149.888</v>
+        <v>299.776</v>
       </c>
       <c r="D54" t="n">
         <v>408</v>
       </c>
       <c r="E54" t="n">
-        <v>368</v>
+        <v>736</v>
       </c>
       <c r="F54" t="n">
-        <v>366.6985294117647</v>
+        <v>733.3970588235294</v>
       </c>
       <c r="G54" t="n">
-        <v>31.49025507848775</v>
+        <v>62.98051015697551</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -4341,19 +4341,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>150.014</v>
+        <v>300.028</v>
       </c>
       <c r="D55" t="n">
         <v>360</v>
       </c>
       <c r="E55" t="n">
-        <v>419.5</v>
+        <v>839</v>
       </c>
       <c r="F55" t="n">
-        <v>415.5527777777778</v>
+        <v>831.1055555555556</v>
       </c>
       <c r="G55" t="n">
-        <v>65.35297341608674</v>
+        <v>130.7059468321735</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -4371,19 +4371,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>149.772</v>
+        <v>299.544</v>
       </c>
       <c r="D56" t="n">
         <v>436</v>
       </c>
       <c r="E56" t="n">
-        <v>344.5</v>
+        <v>689</v>
       </c>
       <c r="F56" t="n">
-        <v>342.7064220183486</v>
+        <v>685.4128440366973</v>
       </c>
       <c r="G56" t="n">
-        <v>27.55869064246772</v>
+        <v>55.11738128493545</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -4401,19 +4401,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>150.199</v>
+        <v>300.398</v>
       </c>
       <c r="D57" t="n">
         <v>423</v>
       </c>
       <c r="E57" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="F57" t="n">
-        <v>354.2387706855792</v>
+        <v>708.4775413711584</v>
       </c>
       <c r="G57" t="n">
-        <v>92.43833456452688</v>
+        <v>184.8766691290538</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>149.747</v>
+        <v>299.494</v>
       </c>
       <c r="D58" t="n">
         <v>376</v>
       </c>
       <c r="E58" t="n">
-        <v>405</v>
+        <v>810</v>
       </c>
       <c r="F58" t="n">
-        <v>397.2792553191489</v>
+        <v>794.5585106382979</v>
       </c>
       <c r="G58" t="n">
-        <v>42.95596747652149</v>
+        <v>85.91193495304297</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>149.976</v>
+        <v>299.952</v>
       </c>
       <c r="D59" t="n">
         <v>443</v>
       </c>
       <c r="E59" t="n">
-        <v>337</v>
+        <v>674</v>
       </c>
       <c r="F59" t="n">
-        <v>337.9006772009029</v>
+        <v>675.8013544018058</v>
       </c>
       <c r="G59" t="n">
-        <v>34.07343778423729</v>
+        <v>68.14687556847457</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -4491,19 +4491,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>150.182</v>
+        <v>300.364</v>
       </c>
       <c r="D60" t="n">
         <v>377</v>
       </c>
       <c r="E60" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="F60" t="n">
-        <v>397.7294429708223</v>
+        <v>795.4588859416446</v>
       </c>
       <c r="G60" t="n">
-        <v>29.73430227649111</v>
+        <v>59.46860455298222</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -4521,19 +4521,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>150.158</v>
+        <v>300.316</v>
       </c>
       <c r="D61" t="n">
         <v>413</v>
       </c>
       <c r="E61" t="n">
-        <v>362</v>
+        <v>724</v>
       </c>
       <c r="F61" t="n">
-        <v>363.09200968523</v>
+        <v>726.1840193704601</v>
       </c>
       <c r="G61" t="n">
-        <v>24.3624782939106</v>
+        <v>48.7249565878212</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -4551,19 +4551,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>149.651</v>
+        <v>299.302</v>
       </c>
       <c r="D62" t="n">
         <v>421</v>
       </c>
       <c r="E62" t="n">
-        <v>349</v>
+        <v>698</v>
       </c>
       <c r="F62" t="n">
-        <v>354.8218527315914</v>
+        <v>709.6437054631829</v>
       </c>
       <c r="G62" t="n">
-        <v>49.04020796766255</v>
+        <v>98.08041593532511</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -4581,19 +4581,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>150.053</v>
+        <v>300.106</v>
       </c>
       <c r="D63" t="n">
         <v>415</v>
       </c>
       <c r="E63" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="F63" t="n">
-        <v>360.7710843373494</v>
+        <v>721.5421686746988</v>
       </c>
       <c r="G63" t="n">
-        <v>26.46313875165772</v>
+        <v>52.92627750331543</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -4611,19 +4611,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>53.334</v>
+        <v>106.668</v>
       </c>
       <c r="D64" t="n">
         <v>122</v>
       </c>
       <c r="E64" t="n">
-        <v>421.5</v>
+        <v>843</v>
       </c>
       <c r="F64" t="n">
-        <v>434.8606557377049</v>
+        <v>869.7213114754098</v>
       </c>
       <c r="G64" t="n">
-        <v>41.64615120644711</v>
+        <v>83.29230241289422</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4641,19 +4641,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>150.185</v>
+        <v>300.37</v>
       </c>
       <c r="D65" t="n">
         <v>368</v>
       </c>
       <c r="E65" t="n">
-        <v>405.5</v>
+        <v>811</v>
       </c>
       <c r="F65" t="n">
-        <v>407.5570652173913</v>
+        <v>815.1141304347826</v>
       </c>
       <c r="G65" t="n">
-        <v>73.11736676907677</v>
+        <v>146.2347335381535</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -4671,19 +4671,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>150.171</v>
+        <v>300.342</v>
       </c>
       <c r="D66" t="n">
         <v>393</v>
       </c>
       <c r="E66" t="n">
-        <v>378</v>
+        <v>756</v>
       </c>
       <c r="F66" t="n">
-        <v>381.027989821883</v>
+        <v>762.0559796437659</v>
       </c>
       <c r="G66" t="n">
-        <v>52.94241895470405</v>
+        <v>105.8848379094081</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>87.577</v>
+        <v>175.154</v>
       </c>
       <c r="D67" t="n">
         <v>235</v>
       </c>
       <c r="E67" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="F67" t="n">
-        <v>371.4978723404255</v>
+        <v>742.9957446808511</v>
       </c>
       <c r="G67" t="n">
-        <v>79.24280411495246</v>
+        <v>158.4856082299049</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -4731,19 +4731,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>149.774</v>
+        <v>299.548</v>
       </c>
       <c r="D68" t="n">
         <v>494</v>
       </c>
       <c r="E68" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F68" t="n">
-        <v>302.6538461538461</v>
+        <v>605.3076923076923</v>
       </c>
       <c r="G68" t="n">
-        <v>29.64200899305984</v>
+        <v>59.28401798611967</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4761,19 +4761,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>60.132</v>
+        <v>120.264</v>
       </c>
       <c r="D69" t="n">
         <v>158</v>
       </c>
       <c r="E69" t="n">
-        <v>376</v>
+        <v>752</v>
       </c>
       <c r="F69" t="n">
-        <v>377.7594936708861</v>
+        <v>755.5189873417721</v>
       </c>
       <c r="G69" t="n">
-        <v>57.8774710996299</v>
+        <v>115.7549421992598</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4791,19 +4791,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>85.892</v>
+        <v>171.784</v>
       </c>
       <c r="D70" t="n">
         <v>212</v>
       </c>
       <c r="E70" t="n">
-        <v>396</v>
+        <v>792</v>
       </c>
       <c r="F70" t="n">
-        <v>401.1981132075472</v>
+        <v>802.3962264150944</v>
       </c>
       <c r="G70" t="n">
-        <v>78.12475377766798</v>
+        <v>156.249507555336</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4821,19 +4821,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>150.076</v>
+        <v>300.152</v>
       </c>
       <c r="D71" t="n">
         <v>448</v>
       </c>
       <c r="E71" t="n">
-        <v>331</v>
+        <v>662</v>
       </c>
       <c r="F71" t="n">
-        <v>334.6339285714286</v>
+        <v>669.2678571428571</v>
       </c>
       <c r="G71" t="n">
-        <v>36.65816347261607</v>
+        <v>73.31632694523215</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -4851,19 +4851,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>110.273</v>
+        <v>220.546</v>
       </c>
       <c r="D72" t="n">
         <v>294</v>
       </c>
       <c r="E72" t="n">
-        <v>375.5</v>
+        <v>751</v>
       </c>
       <c r="F72" t="n">
-        <v>373.2993197278911</v>
+        <v>746.5986394557823</v>
       </c>
       <c r="G72" t="n">
-        <v>80.39687520170027</v>
+        <v>160.7937504034005</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -4881,19 +4881,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>150.408</v>
+        <v>300.816</v>
       </c>
       <c r="D73" t="n">
         <v>435</v>
       </c>
       <c r="E73" t="n">
-        <v>344</v>
+        <v>688</v>
       </c>
       <c r="F73" t="n">
-        <v>345.3632183908046</v>
+        <v>690.7264367816092</v>
       </c>
       <c r="G73" t="n">
-        <v>24.61990369235548</v>
+        <v>49.23980738471096</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -4911,19 +4911,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>149.955</v>
+        <v>299.91</v>
       </c>
       <c r="D74" t="n">
         <v>373</v>
       </c>
       <c r="E74" t="n">
-        <v>393</v>
+        <v>786</v>
       </c>
       <c r="F74" t="n">
-        <v>401.4021447721179</v>
+        <v>802.8042895442359</v>
       </c>
       <c r="G74" t="n">
-        <v>48.45920793922723</v>
+        <v>96.91841587845447</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -4941,19 +4941,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>103.611</v>
+        <v>207.222</v>
       </c>
       <c r="D75" t="n">
         <v>236</v>
       </c>
       <c r="E75" t="n">
-        <v>419.5</v>
+        <v>839</v>
       </c>
       <c r="F75" t="n">
-        <v>433.4322033898305</v>
+        <v>866.8644067796611</v>
       </c>
       <c r="G75" t="n">
-        <v>142.6320353627479</v>
+        <v>285.2640707254957</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -4971,19 +4971,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>150.426</v>
+        <v>300.852</v>
       </c>
       <c r="D76" t="n">
         <v>362</v>
       </c>
       <c r="E76" t="n">
-        <v>419</v>
+        <v>838</v>
       </c>
       <c r="F76" t="n">
-        <v>414.2707182320442</v>
+        <v>828.5414364640884</v>
       </c>
       <c r="G76" t="n">
-        <v>94.12947806924235</v>
+        <v>188.2589561384847</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -5001,19 +5001,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>104.019</v>
+        <v>208.038</v>
       </c>
       <c r="D77" t="n">
         <v>316</v>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>616</v>
       </c>
       <c r="F77" t="n">
-        <v>327.7721518987342</v>
+        <v>655.5443037974684</v>
       </c>
       <c r="G77" t="n">
-        <v>67.43913410863817</v>
+        <v>134.8782682172763</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -5031,19 +5031,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>150.097</v>
+        <v>300.194</v>
       </c>
       <c r="D78" t="n">
         <v>331</v>
       </c>
       <c r="E78" t="n">
-        <v>456</v>
+        <v>912</v>
       </c>
       <c r="F78" t="n">
-        <v>452.619335347432</v>
+        <v>905.238670694864</v>
       </c>
       <c r="G78" t="n">
-        <v>62.22476453937885</v>
+        <v>124.4495290787577</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -5061,19 +5061,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>160.906</v>
+        <v>321.812</v>
       </c>
       <c r="D79" t="n">
         <v>397</v>
       </c>
       <c r="E79" t="n">
-        <v>405</v>
+        <v>810</v>
       </c>
       <c r="F79" t="n">
-        <v>404.7758186397985</v>
+        <v>809.551637279597</v>
       </c>
       <c r="G79" t="n">
-        <v>30.03529270249586</v>
+        <v>60.07058540499172</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -5142,19 +5142,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>75.029</v>
+        <v>150.058</v>
       </c>
       <c r="D2" t="n">
         <v>346</v>
       </c>
       <c r="E2" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F2" t="n">
-        <v>216.3381502890173</v>
+        <v>432.6763005780347</v>
       </c>
       <c r="G2" t="n">
-        <v>21.38097735162453</v>
+        <v>42.76195470324906</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -5172,19 +5172,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>71.929</v>
+        <v>143.858</v>
       </c>
       <c r="D3" t="n">
         <v>332</v>
       </c>
       <c r="E3" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F3" t="n">
-        <v>215.9036144578313</v>
+        <v>431.8072289156627</v>
       </c>
       <c r="G3" t="n">
-        <v>17.64614553246751</v>
+        <v>35.29229106493501</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -5202,19 +5202,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.08799999999999</v>
+        <v>150.176</v>
       </c>
       <c r="D4" t="n">
         <v>334</v>
       </c>
       <c r="E4" t="n">
-        <v>223</v>
+        <v>446</v>
       </c>
       <c r="F4" t="n">
-        <v>224.1796407185629</v>
+        <v>448.3592814371257</v>
       </c>
       <c r="G4" t="n">
-        <v>13.64139847754188</v>
+        <v>27.28279695508375</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -5232,19 +5232,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.973</v>
+        <v>149.946</v>
       </c>
       <c r="D5" t="n">
         <v>369</v>
       </c>
       <c r="E5" t="n">
-        <v>201</v>
+        <v>402</v>
       </c>
       <c r="F5" t="n">
-        <v>202.6476964769648</v>
+        <v>405.2953929539295</v>
       </c>
       <c r="G5" t="n">
-        <v>13.81773833799108</v>
+        <v>27.63547667598217</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5262,19 +5262,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.12</v>
+        <v>150.24</v>
       </c>
       <c r="D6" t="n">
         <v>356</v>
       </c>
       <c r="E6" t="n">
-        <v>207</v>
+        <v>414</v>
       </c>
       <c r="F6" t="n">
-        <v>210.2219101123596</v>
+        <v>420.4438202247191</v>
       </c>
       <c r="G6" t="n">
-        <v>22.41374509757215</v>
+        <v>44.8274901951443</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -5292,19 +5292,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.953</v>
+        <v>149.906</v>
       </c>
       <c r="D7" t="n">
         <v>338</v>
       </c>
       <c r="E7" t="n">
-        <v>217</v>
+        <v>434</v>
       </c>
       <c r="F7" t="n">
-        <v>220.9230769230769</v>
+        <v>441.8461538461539</v>
       </c>
       <c r="G7" t="n">
-        <v>36.46892095806643</v>
+        <v>72.93784191613287</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5322,19 +5322,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33.63</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>345.5</v>
+        <v>691</v>
       </c>
       <c r="F8" t="n">
-        <v>346.5625</v>
+        <v>693.125</v>
       </c>
       <c r="G8" t="n">
-        <v>30.32032929275427</v>
+        <v>60.64065858550854</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -5352,19 +5352,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.97499999999999</v>
+        <v>149.95</v>
       </c>
       <c r="D9" t="n">
         <v>344</v>
       </c>
       <c r="E9" t="n">
-        <v>218</v>
+        <v>436</v>
       </c>
       <c r="F9" t="n">
-        <v>217.1831395348837</v>
+        <v>434.3662790697674</v>
       </c>
       <c r="G9" t="n">
-        <v>14.60015797363538</v>
+        <v>29.20031594727077</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5382,19 +5382,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>75.02800000000001</v>
+        <v>150.056</v>
       </c>
       <c r="D10" t="n">
         <v>330</v>
       </c>
       <c r="E10" t="n">
-        <v>222</v>
+        <v>444</v>
       </c>
       <c r="F10" t="n">
-        <v>226.2333333333333</v>
+        <v>452.4666666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>18.52206712594559</v>
+        <v>37.04413425189119</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5412,19 +5412,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.10299999999999</v>
+        <v>150.206</v>
       </c>
       <c r="D11" t="n">
         <v>292</v>
       </c>
       <c r="E11" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="F11" t="n">
-        <v>256.0034246575343</v>
+        <v>512.0068493150685</v>
       </c>
       <c r="G11" t="n">
-        <v>39.23569612960082</v>
+        <v>78.47139225920164</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5442,19 +5442,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75.14700000000001</v>
+        <v>150.294</v>
       </c>
       <c r="D12" t="n">
         <v>305</v>
       </c>
       <c r="E12" t="n">
-        <v>246</v>
+        <v>492</v>
       </c>
       <c r="F12" t="n">
-        <v>245.7573770491803</v>
+        <v>491.5147540983606</v>
       </c>
       <c r="G12" t="n">
-        <v>16.21809072553574</v>
+        <v>32.43618145107148</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5472,19 +5472,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74.985</v>
+        <v>149.97</v>
       </c>
       <c r="D13" t="n">
         <v>329</v>
       </c>
       <c r="E13" t="n">
-        <v>229</v>
+        <v>458</v>
       </c>
       <c r="F13" t="n">
-        <v>227.1489361702128</v>
+        <v>454.2978723404256</v>
       </c>
       <c r="G13" t="n">
-        <v>14.1477075329534</v>
+        <v>28.29541506590681</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5502,19 +5502,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75.36199999999999</v>
+        <v>150.724</v>
       </c>
       <c r="D14" t="n">
         <v>333</v>
       </c>
       <c r="E14" t="n">
-        <v>224</v>
+        <v>448</v>
       </c>
       <c r="F14" t="n">
-        <v>225.7807807807808</v>
+        <v>451.5615615615616</v>
       </c>
       <c r="G14" t="n">
-        <v>16.90164647616949</v>
+        <v>33.80329295233899</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5532,19 +5532,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>74.991</v>
+        <v>149.982</v>
       </c>
       <c r="D15" t="n">
         <v>367</v>
       </c>
       <c r="E15" t="n">
-        <v>199</v>
+        <v>398</v>
       </c>
       <c r="F15" t="n">
-        <v>203.9237057220708</v>
+        <v>407.8474114441417</v>
       </c>
       <c r="G15" t="n">
-        <v>20.55233648186949</v>
+        <v>41.10467296373898</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5562,19 +5562,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74.91</v>
+        <v>149.82</v>
       </c>
       <c r="D16" t="n">
         <v>345</v>
       </c>
       <c r="E16" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F16" t="n">
-        <v>216.2086956521739</v>
+        <v>432.4173913043478</v>
       </c>
       <c r="G16" t="n">
-        <v>22.05390949845002</v>
+        <v>44.10781899690004</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5592,19 +5592,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74.997</v>
+        <v>149.994</v>
       </c>
       <c r="D17" t="n">
         <v>314</v>
       </c>
       <c r="E17" t="n">
-        <v>237</v>
+        <v>474</v>
       </c>
       <c r="F17" t="n">
-        <v>237.6656050955414</v>
+        <v>475.3312101910828</v>
       </c>
       <c r="G17" t="n">
-        <v>14.59417894975096</v>
+        <v>29.18835789950193</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5622,19 +5622,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36.643</v>
+        <v>73.286</v>
       </c>
       <c r="D18" t="n">
         <v>164</v>
       </c>
       <c r="E18" t="n">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="F18" t="n">
-        <v>222.4207317073171</v>
+        <v>444.8414634146341</v>
       </c>
       <c r="G18" t="n">
-        <v>38.55567001439433</v>
+        <v>77.11134002878866</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -5652,19 +5652,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>75.127</v>
+        <v>150.254</v>
       </c>
       <c r="D19" t="n">
         <v>320</v>
       </c>
       <c r="E19" t="n">
-        <v>235</v>
+        <v>470</v>
       </c>
       <c r="F19" t="n">
-        <v>234.275</v>
+        <v>468.55</v>
       </c>
       <c r="G19" t="n">
-        <v>15.10027091870149</v>
+        <v>30.20054183740297</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -5682,19 +5682,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>75.10299999999999</v>
+        <v>150.206</v>
       </c>
       <c r="D20" t="n">
         <v>353</v>
       </c>
       <c r="E20" t="n">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="F20" t="n">
-        <v>212.1501416430595</v>
+        <v>424.300283286119</v>
       </c>
       <c r="G20" t="n">
-        <v>18.9012868198382</v>
+        <v>37.8025736396764</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -5712,19 +5712,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75.011</v>
+        <v>150.022</v>
       </c>
       <c r="D21" t="n">
         <v>327</v>
       </c>
       <c r="E21" t="n">
-        <v>219</v>
+        <v>438</v>
       </c>
       <c r="F21" t="n">
-        <v>228.4678899082569</v>
+        <v>456.9357798165138</v>
       </c>
       <c r="G21" t="n">
-        <v>52.6448749783374</v>
+        <v>105.2897499566748</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -5742,19 +5742,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>74.70699999999999</v>
+        <v>149.414</v>
       </c>
       <c r="D22" t="n">
         <v>352</v>
       </c>
       <c r="E22" t="n">
-        <v>206</v>
+        <v>412</v>
       </c>
       <c r="F22" t="n">
-        <v>211.5568181818182</v>
+        <v>423.1136363636364</v>
       </c>
       <c r="G22" t="n">
-        <v>33.51076127859708</v>
+        <v>67.02152255719416</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -5772,19 +5772,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.189</v>
+        <v>114.378</v>
       </c>
       <c r="D23" t="n">
         <v>275</v>
       </c>
       <c r="E23" t="n">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="F23" t="n">
-        <v>206.9454545454545</v>
+        <v>413.8909090909091</v>
       </c>
       <c r="G23" t="n">
-        <v>22.91942262891889</v>
+        <v>45.83884525783778</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -5802,19 +5802,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74.94799999999999</v>
+        <v>149.896</v>
       </c>
       <c r="D24" t="n">
         <v>351</v>
       </c>
       <c r="E24" t="n">
-        <v>207</v>
+        <v>414</v>
       </c>
       <c r="F24" t="n">
-        <v>212.7606837606837</v>
+        <v>425.5213675213675</v>
       </c>
       <c r="G24" t="n">
-        <v>35.97451071585854</v>
+        <v>71.94902143171709</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -5832,19 +5832,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>75.08799999999999</v>
+        <v>150.176</v>
       </c>
       <c r="D25" t="n">
         <v>328</v>
       </c>
       <c r="E25" t="n">
-        <v>227</v>
+        <v>454</v>
       </c>
       <c r="F25" t="n">
-        <v>228.3201219512195</v>
+        <v>456.640243902439</v>
       </c>
       <c r="G25" t="n">
-        <v>13.39329641932516</v>
+        <v>26.78659283865032</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -5862,19 +5862,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>74.93899999999999</v>
+        <v>149.878</v>
       </c>
       <c r="D26" t="n">
         <v>316</v>
       </c>
       <c r="E26" t="n">
-        <v>231</v>
+        <v>462</v>
       </c>
       <c r="F26" t="n">
-        <v>236.2373417721519</v>
+        <v>472.4746835443038</v>
       </c>
       <c r="G26" t="n">
-        <v>33.255012719989</v>
+        <v>66.51002543997801</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -5892,19 +5892,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>75.03400000000001</v>
+        <v>150.068</v>
       </c>
       <c r="D27" t="n">
         <v>309</v>
       </c>
       <c r="E27" t="n">
-        <v>242</v>
+        <v>484</v>
       </c>
       <c r="F27" t="n">
-        <v>242.0291262135922</v>
+        <v>484.0582524271845</v>
       </c>
       <c r="G27" t="n">
-        <v>13.66846995779941</v>
+        <v>27.33693991559883</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>51.12</v>
+        <v>102.24</v>
       </c>
       <c r="D28" t="n">
         <v>227</v>
       </c>
       <c r="E28" t="n">
-        <v>222</v>
+        <v>444</v>
       </c>
       <c r="F28" t="n">
-        <v>223.9559471365639</v>
+        <v>447.9118942731278</v>
       </c>
       <c r="G28" t="n">
-        <v>20.12764130651092</v>
+        <v>40.25528261302185</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -5952,19 +5952,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>75.06100000000001</v>
+        <v>150.122</v>
       </c>
       <c r="D29" t="n">
         <v>400</v>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="F29" t="n">
-        <v>187.2275</v>
+        <v>374.455</v>
       </c>
       <c r="G29" t="n">
-        <v>15.9033970851236</v>
+        <v>31.8067941702472</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -5982,19 +5982,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>74.916</v>
+        <v>149.832</v>
       </c>
       <c r="D30" t="n">
         <v>303</v>
       </c>
       <c r="E30" t="n">
-        <v>243</v>
+        <v>486</v>
       </c>
       <c r="F30" t="n">
-        <v>246.5445544554455</v>
+        <v>493.0891089108911</v>
       </c>
       <c r="G30" t="n">
-        <v>23.43987295377072</v>
+        <v>46.87974590754144</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -6012,19 +6012,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>74.941</v>
+        <v>149.882</v>
       </c>
       <c r="D31" t="n">
         <v>320</v>
       </c>
       <c r="E31" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F31" t="n">
-        <v>233.603125</v>
+        <v>467.20625</v>
       </c>
       <c r="G31" t="n">
-        <v>16.76974781010198</v>
+        <v>33.53949562020396</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -6042,19 +6042,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>75.002</v>
+        <v>150.004</v>
       </c>
       <c r="D32" t="n">
         <v>327</v>
       </c>
       <c r="E32" t="n">
-        <v>229</v>
+        <v>458</v>
       </c>
       <c r="F32" t="n">
-        <v>228.4067278287462</v>
+        <v>456.8134556574923</v>
       </c>
       <c r="G32" t="n">
-        <v>17.75661159148816</v>
+        <v>35.51322318297632</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>75.09999999999999</v>
+        <v>150.2</v>
       </c>
       <c r="D33" t="n">
         <v>414</v>
       </c>
       <c r="E33" t="n">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="F33" t="n">
-        <v>181.0024154589372</v>
+        <v>362.0048309178744</v>
       </c>
       <c r="G33" t="n">
-        <v>27.79712901651234</v>
+        <v>55.59425803302468</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -6102,19 +6102,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>71.38</v>
+        <v>142.76</v>
       </c>
       <c r="D34" t="n">
         <v>306</v>
       </c>
       <c r="E34" t="n">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="F34" t="n">
-        <v>232.718954248366</v>
+        <v>465.437908496732</v>
       </c>
       <c r="G34" t="n">
-        <v>37.63342733094223</v>
+        <v>75.26685466188447</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6132,19 +6132,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>74.497</v>
+        <v>148.994</v>
       </c>
       <c r="D35" t="n">
         <v>116</v>
       </c>
       <c r="E35" t="n">
-        <v>632</v>
+        <v>1264</v>
       </c>
       <c r="F35" t="n">
-        <v>639.5775862068965</v>
+        <v>1279.155172413793</v>
       </c>
       <c r="G35" t="n">
-        <v>271.3847309428177</v>
+        <v>542.7694618856353</v>
       </c>
       <c r="H35" t="n">
         <v>77</v>
@@ -6162,19 +6162,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15.992</v>
+        <v>31.984</v>
       </c>
       <c r="D36" t="n">
         <v>74</v>
       </c>
       <c r="E36" t="n">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="F36" t="n">
-        <v>212.6081081081081</v>
+        <v>425.2162162162162</v>
       </c>
       <c r="G36" t="n">
-        <v>32.1962380034872</v>
+        <v>64.39247600697441</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -6192,19 +6192,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>75.252</v>
+        <v>150.504</v>
       </c>
       <c r="D37" t="n">
         <v>345</v>
       </c>
       <c r="E37" t="n">
-        <v>211</v>
+        <v>422</v>
       </c>
       <c r="F37" t="n">
-        <v>217.3855072463768</v>
+        <v>434.7710144927536</v>
       </c>
       <c r="G37" t="n">
-        <v>31.24628943255502</v>
+        <v>62.49257886511005</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -6222,19 +6222,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>74.925</v>
+        <v>149.85</v>
       </c>
       <c r="D38" t="n">
         <v>336</v>
       </c>
       <c r="E38" t="n">
-        <v>219</v>
+        <v>438</v>
       </c>
       <c r="F38" t="n">
-        <v>221.8809523809524</v>
+        <v>443.7619047619048</v>
       </c>
       <c r="G38" t="n">
-        <v>29.0904527650454</v>
+        <v>58.1809055300908</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -6252,19 +6252,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>75.122</v>
+        <v>150.244</v>
       </c>
       <c r="D39" t="n">
         <v>345</v>
       </c>
       <c r="E39" t="n">
-        <v>217</v>
+        <v>434</v>
       </c>
       <c r="F39" t="n">
-        <v>217.2666666666667</v>
+        <v>434.5333333333334</v>
       </c>
       <c r="G39" t="n">
-        <v>9.775007682544217</v>
+        <v>19.55001536508843</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -6282,19 +6282,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64.42</v>
+        <v>128.84</v>
       </c>
       <c r="D40" t="n">
         <v>267</v>
       </c>
       <c r="E40" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F40" t="n">
-        <v>240.0674157303371</v>
+        <v>480.1348314606741</v>
       </c>
       <c r="G40" t="n">
-        <v>34.97694119669264</v>
+        <v>69.95388239338527</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -6312,19 +6312,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>74.935</v>
+        <v>149.87</v>
       </c>
       <c r="D41" t="n">
         <v>367</v>
       </c>
       <c r="E41" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F41" t="n">
-        <v>203.6130790190736</v>
+        <v>407.2261580381472</v>
       </c>
       <c r="G41" t="n">
-        <v>33.89565542790376</v>
+        <v>67.79131085580752</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -6342,19 +6342,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>74.964</v>
+        <v>149.928</v>
       </c>
       <c r="D42" t="n">
         <v>320</v>
       </c>
       <c r="E42" t="n">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="F42" t="n">
-        <v>233.5</v>
+        <v>467</v>
       </c>
       <c r="G42" t="n">
-        <v>21.31536599700336</v>
+        <v>42.63073199400672</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -6372,19 +6372,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>74.884</v>
+        <v>149.768</v>
       </c>
       <c r="D43" t="n">
         <v>327</v>
       </c>
       <c r="E43" t="n">
-        <v>219</v>
+        <v>438</v>
       </c>
       <c r="F43" t="n">
-        <v>223.4648318042813</v>
+        <v>446.9296636085627</v>
       </c>
       <c r="G43" t="n">
-        <v>31.28972790369987</v>
+        <v>62.57945580739974</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -6402,19 +6402,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33.912</v>
+        <v>67.824</v>
       </c>
       <c r="D44" t="n">
         <v>168</v>
       </c>
       <c r="E44" t="n">
-        <v>193.5</v>
+        <v>387</v>
       </c>
       <c r="F44" t="n">
-        <v>199.7261904761905</v>
+        <v>399.452380952381</v>
       </c>
       <c r="G44" t="n">
-        <v>19.36559773980109</v>
+        <v>38.73119547960218</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -6432,19 +6432,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>74.95099999999999</v>
+        <v>149.902</v>
       </c>
       <c r="D45" t="n">
         <v>329</v>
       </c>
       <c r="E45" t="n">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="F45" t="n">
-        <v>227.0334346504559</v>
+        <v>454.0668693009118</v>
       </c>
       <c r="G45" t="n">
-        <v>21.69639681637372</v>
+        <v>43.39279363274744</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -6462,19 +6462,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>75.181</v>
+        <v>150.362</v>
       </c>
       <c r="D46" t="n">
         <v>344</v>
       </c>
       <c r="E46" t="n">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="F46" t="n">
-        <v>217.7558139534884</v>
+        <v>435.5116279069767</v>
       </c>
       <c r="G46" t="n">
-        <v>12.72557265255863</v>
+        <v>25.45114530511727</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -6492,19 +6492,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>74.90300000000001</v>
+        <v>149.806</v>
       </c>
       <c r="D47" t="n">
         <v>318</v>
       </c>
       <c r="E47" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F47" t="n">
-        <v>234.748427672956</v>
+        <v>469.496855345912</v>
       </c>
       <c r="G47" t="n">
-        <v>23.90384749292013</v>
+        <v>47.80769498584025</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -6522,19 +6522,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>74.923</v>
+        <v>149.846</v>
       </c>
       <c r="D48" t="n">
         <v>313</v>
       </c>
       <c r="E48" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F48" t="n">
-        <v>238.2715654952077</v>
+        <v>476.5431309904154</v>
       </c>
       <c r="G48" t="n">
-        <v>19.27748761200777</v>
+        <v>38.55497522401555</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -6552,19 +6552,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69.41800000000001</v>
+        <v>138.836</v>
       </c>
       <c r="D49" t="n">
         <v>321</v>
       </c>
       <c r="E49" t="n">
-        <v>214</v>
+        <v>428</v>
       </c>
       <c r="F49" t="n">
-        <v>215.5545171339564</v>
+        <v>431.1090342679128</v>
       </c>
       <c r="G49" t="n">
-        <v>23.57059184331689</v>
+        <v>47.14118368663378</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -6582,19 +6582,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>75.119</v>
+        <v>150.238</v>
       </c>
       <c r="D50" t="n">
         <v>357</v>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="F50" t="n">
-        <v>209.8739495798319</v>
+        <v>419.7478991596639</v>
       </c>
       <c r="G50" t="n">
-        <v>7.689429438348356</v>
+        <v>15.37885887669671</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -6612,19 +6612,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>75.057</v>
+        <v>150.114</v>
       </c>
       <c r="D51" t="n">
         <v>365</v>
       </c>
       <c r="E51" t="n">
-        <v>197</v>
+        <v>394</v>
       </c>
       <c r="F51" t="n">
-        <v>204.8657534246575</v>
+        <v>409.7315068493151</v>
       </c>
       <c r="G51" t="n">
-        <v>24.45484861235742</v>
+        <v>48.90969722471483</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -6642,19 +6642,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>68.74299999999999</v>
+        <v>137.486</v>
       </c>
       <c r="D52" t="n">
         <v>342</v>
       </c>
       <c r="E52" t="n">
-        <v>201</v>
+        <v>402</v>
       </c>
       <c r="F52" t="n">
-        <v>200.219298245614</v>
+        <v>400.4385964912281</v>
       </c>
       <c r="G52" t="n">
-        <v>30.6942424239656</v>
+        <v>61.38848484793121</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -6672,19 +6672,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>74.937</v>
+        <v>149.874</v>
       </c>
       <c r="D53" t="n">
         <v>392</v>
       </c>
       <c r="E53" t="n">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="F53" t="n">
-        <v>190.3801020408163</v>
+        <v>380.7602040816327</v>
       </c>
       <c r="G53" t="n">
-        <v>28.59830109578204</v>
+        <v>57.19660219156409</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -6702,19 +6702,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>67.76600000000001</v>
+        <v>135.532</v>
       </c>
       <c r="D54" t="n">
         <v>320</v>
       </c>
       <c r="E54" t="n">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="F54" t="n">
-        <v>210.890625</v>
+        <v>421.78125</v>
       </c>
       <c r="G54" t="n">
-        <v>39.63853812815634</v>
+        <v>79.27707625631268</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -6732,19 +6732,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>75.051</v>
+        <v>150.102</v>
       </c>
       <c r="D55" t="n">
         <v>335</v>
       </c>
       <c r="E55" t="n">
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="F55" t="n">
-        <v>223.0746268656716</v>
+        <v>446.1492537313433</v>
       </c>
       <c r="G55" t="n">
-        <v>33.83949143565587</v>
+        <v>67.67898287131175</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -6762,19 +6762,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>75.11</v>
+        <v>150.22</v>
       </c>
       <c r="D56" t="n">
         <v>359</v>
       </c>
       <c r="E56" t="n">
-        <v>202</v>
+        <v>404</v>
       </c>
       <c r="F56" t="n">
-        <v>208.5849582172702</v>
+        <v>417.1699164345404</v>
       </c>
       <c r="G56" t="n">
-        <v>37.22043496117914</v>
+        <v>74.44086992235827</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -6792,19 +6792,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>61.216</v>
+        <v>122.432</v>
       </c>
       <c r="D57" t="n">
         <v>242</v>
       </c>
       <c r="E57" t="n">
-        <v>217</v>
+        <v>434</v>
       </c>
       <c r="F57" t="n">
-        <v>217.6322314049587</v>
+        <v>435.2644628099173</v>
       </c>
       <c r="G57" t="n">
-        <v>6.436497525390835</v>
+        <v>12.87299505078167</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -6822,19 +6822,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>75.45999999999999</v>
+        <v>150.92</v>
       </c>
       <c r="D58" t="n">
         <v>348</v>
       </c>
       <c r="E58" t="n">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="F58" t="n">
-        <v>215.8304597701149</v>
+        <v>431.6609195402299</v>
       </c>
       <c r="G58" t="n">
-        <v>20.6571433400061</v>
+        <v>41.3142866800122</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -6852,19 +6852,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>74.821</v>
+        <v>149.642</v>
       </c>
       <c r="D59" t="n">
         <v>313</v>
       </c>
       <c r="E59" t="n">
-        <v>239</v>
+        <v>478</v>
       </c>
       <c r="F59" t="n">
-        <v>238.2555910543131</v>
+        <v>476.5111821086262</v>
       </c>
       <c r="G59" t="n">
-        <v>10.91921863628983</v>
+        <v>21.83843727257967</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>74.996</v>
+        <v>149.992</v>
       </c>
       <c r="D60" t="n">
         <v>336</v>
       </c>
       <c r="E60" t="n">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="F60" t="n">
-        <v>222.672619047619</v>
+        <v>445.3452380952381</v>
       </c>
       <c r="G60" t="n">
-        <v>17.65929530677977</v>
+        <v>35.31859061355954</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -6912,19 +6912,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>93.07899999999999</v>
+        <v>186.158</v>
       </c>
       <c r="D61" t="n">
         <v>382</v>
       </c>
       <c r="E61" t="n">
-        <v>242</v>
+        <v>484</v>
       </c>
       <c r="F61" t="n">
-        <v>243.261780104712</v>
+        <v>486.5235602094241</v>
       </c>
       <c r="G61" t="n">
-        <v>30.96962452173316</v>
+        <v>61.93924904346633</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -6942,19 +6942,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>75.029</v>
+        <v>150.058</v>
       </c>
       <c r="D62" t="n">
         <v>340</v>
       </c>
       <c r="E62" t="n">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="F62" t="n">
-        <v>219.5441176470588</v>
+        <v>439.0882352941176</v>
       </c>
       <c r="G62" t="n">
-        <v>14.48998619078456</v>
+        <v>28.97997238156912</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -6972,19 +6972,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>22.914</v>
+        <v>45.828</v>
       </c>
       <c r="D63" t="n">
         <v>101</v>
       </c>
       <c r="E63" t="n">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="F63" t="n">
-        <v>223.8910891089109</v>
+        <v>447.7821782178218</v>
       </c>
       <c r="G63" t="n">
-        <v>35.82259091414216</v>
+        <v>71.64518182828432</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -7002,19 +7002,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>74.73699999999999</v>
+        <v>149.474</v>
       </c>
       <c r="D64" t="n">
         <v>178</v>
       </c>
       <c r="E64" t="n">
-        <v>415.5</v>
+        <v>831</v>
       </c>
       <c r="F64" t="n">
-        <v>418.9606741573033</v>
+        <v>837.9213483146067</v>
       </c>
       <c r="G64" t="n">
-        <v>137.6827747662704</v>
+        <v>275.3655495325409</v>
       </c>
       <c r="H64" t="n">
         <v>11</v>
@@ -7032,19 +7032,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60.596</v>
+        <v>121.192</v>
       </c>
       <c r="D65" t="n">
         <v>192</v>
       </c>
       <c r="E65" t="n">
-        <v>295</v>
+        <v>590</v>
       </c>
       <c r="F65" t="n">
-        <v>312.90625</v>
+        <v>625.8125</v>
       </c>
       <c r="G65" t="n">
-        <v>109.3175477380256</v>
+        <v>218.6350954760511</v>
       </c>
       <c r="H65" t="n">
         <v>3</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>54.365</v>
+        <v>108.73</v>
       </c>
       <c r="D66" t="n">
         <v>240</v>
       </c>
       <c r="E66" t="n">
-        <v>222.5</v>
+        <v>445</v>
       </c>
       <c r="F66" t="n">
-        <v>225.4583333333333</v>
+        <v>450.9166666666667</v>
       </c>
       <c r="G66" t="n">
-        <v>29.66222562468573</v>
+        <v>59.32445124937146</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -7092,19 +7092,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>49.275</v>
+        <v>98.55</v>
       </c>
       <c r="D67" t="n">
         <v>237</v>
       </c>
       <c r="E67" t="n">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="F67" t="n">
-        <v>206.4894514767932</v>
+        <v>412.9789029535865</v>
       </c>
       <c r="G67" t="n">
-        <v>44.17747449395392</v>
+        <v>88.35494898790783</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -7122,19 +7122,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.504</v>
+        <v>83.008</v>
       </c>
       <c r="D68" t="n">
         <v>166</v>
       </c>
       <c r="E68" t="n">
-        <v>251</v>
+        <v>502</v>
       </c>
       <c r="F68" t="n">
-        <v>248.5722891566265</v>
+        <v>497.144578313253</v>
       </c>
       <c r="G68" t="n">
-        <v>30.36511480551729</v>
+        <v>60.73022961103458</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -7152,19 +7152,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>75.349</v>
+        <v>150.698</v>
       </c>
       <c r="D69" t="n">
         <v>345</v>
       </c>
       <c r="E69" t="n">
-        <v>217</v>
+        <v>434</v>
       </c>
       <c r="F69" t="n">
-        <v>217.3304347826087</v>
+        <v>434.6608695652174</v>
       </c>
       <c r="G69" t="n">
-        <v>7.669846280179111</v>
+        <v>15.33969256035822</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -7182,19 +7182,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>74.956</v>
+        <v>149.912</v>
       </c>
       <c r="D70" t="n">
         <v>345</v>
       </c>
       <c r="E70" t="n">
-        <v>214</v>
+        <v>428</v>
       </c>
       <c r="F70" t="n">
-        <v>216.7884057971015</v>
+        <v>433.5768115942029</v>
       </c>
       <c r="G70" t="n">
-        <v>12.50854982290351</v>
+        <v>25.01709964580701</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -7212,19 +7212,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>52.73</v>
+        <v>105.46</v>
       </c>
       <c r="D71" t="n">
         <v>259</v>
       </c>
       <c r="E71" t="n">
-        <v>201</v>
+        <v>402</v>
       </c>
       <c r="F71" t="n">
-        <v>202.9150579150579</v>
+        <v>405.8301158301159</v>
       </c>
       <c r="G71" t="n">
-        <v>15.94638926277321</v>
+        <v>31.89277852554642</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -7242,19 +7242,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>74.946</v>
+        <v>149.892</v>
       </c>
       <c r="D72" t="n">
         <v>345</v>
       </c>
       <c r="E72" t="n">
-        <v>213</v>
+        <v>426</v>
       </c>
       <c r="F72" t="n">
-        <v>216.7971014492754</v>
+        <v>433.5942028985507</v>
       </c>
       <c r="G72" t="n">
-        <v>18.97809302405788</v>
+        <v>37.95618604811576</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -7272,19 +7272,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74.777</v>
+        <v>149.554</v>
       </c>
       <c r="D73" t="n">
         <v>151</v>
       </c>
       <c r="E73" t="n">
-        <v>473</v>
+        <v>946</v>
       </c>
       <c r="F73" t="n">
-        <v>479.6026490066225</v>
+        <v>959.2052980132451</v>
       </c>
       <c r="G73" t="n">
-        <v>181.2810738225845</v>
+        <v>362.5621476451689</v>
       </c>
       <c r="H73" t="n">
         <v>27</v>
@@ -7302,19 +7302,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>74.94499999999999</v>
+        <v>149.89</v>
       </c>
       <c r="D74" t="n">
         <v>329</v>
       </c>
       <c r="E74" t="n">
-        <v>224</v>
+        <v>448</v>
       </c>
       <c r="F74" t="n">
-        <v>227.1580547112462</v>
+        <v>454.3161094224924</v>
       </c>
       <c r="G74" t="n">
-        <v>17.83475822887329</v>
+        <v>35.66951645774657</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -7332,19 +7332,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>129.012</v>
+        <v>258.024</v>
       </c>
       <c r="D75" t="n">
         <v>544</v>
       </c>
       <c r="E75" t="n">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="F75" t="n">
-        <v>236.5257352941177</v>
+        <v>473.0514705882353</v>
       </c>
       <c r="G75" t="n">
-        <v>23.38010202563422</v>
+        <v>46.76020405126843</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -7413,19 +7413,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74.919</v>
+        <v>149.838</v>
       </c>
       <c r="D2" t="n">
         <v>234</v>
       </c>
       <c r="E2" t="n">
-        <v>318</v>
+        <v>636</v>
       </c>
       <c r="F2" t="n">
-        <v>319.3034188034188</v>
+        <v>638.6068376068376</v>
       </c>
       <c r="G2" t="n">
-        <v>34.5661930938282</v>
+        <v>69.13238618765641</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -7443,19 +7443,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>71.76300000000001</v>
+        <v>143.526</v>
       </c>
       <c r="D3" t="n">
         <v>188</v>
       </c>
       <c r="E3" t="n">
-        <v>367.5</v>
+        <v>735</v>
       </c>
       <c r="F3" t="n">
-        <v>380.6117021276596</v>
+        <v>761.2234042553191</v>
       </c>
       <c r="G3" t="n">
-        <v>86.06193063781836</v>
+        <v>172.1238612756367</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7473,19 +7473,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.18000000000001</v>
+        <v>150.36</v>
       </c>
       <c r="D4" t="n">
         <v>286</v>
       </c>
       <c r="E4" t="n">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="F4" t="n">
-        <v>261.9475524475524</v>
+        <v>523.8951048951049</v>
       </c>
       <c r="G4" t="n">
-        <v>20.10134090724222</v>
+        <v>40.20268181448444</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -7503,19 +7503,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.801</v>
+        <v>149.602</v>
       </c>
       <c r="D5" t="n">
         <v>224</v>
       </c>
       <c r="E5" t="n">
-        <v>333</v>
+        <v>666</v>
       </c>
       <c r="F5" t="n">
-        <v>332.9241071428572</v>
+        <v>665.8482142857143</v>
       </c>
       <c r="G5" t="n">
-        <v>28.33398740467989</v>
+        <v>56.66797480935978</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -7533,19 +7533,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.123</v>
+        <v>150.246</v>
       </c>
       <c r="D6" t="n">
         <v>186</v>
       </c>
       <c r="E6" t="n">
-        <v>405.5</v>
+        <v>811</v>
       </c>
       <c r="F6" t="n">
-        <v>401.3279569892473</v>
+        <v>802.6559139784946</v>
       </c>
       <c r="G6" t="n">
-        <v>33.68109539719421</v>
+        <v>67.36219079438841</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -7563,19 +7563,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.755</v>
+        <v>149.51</v>
       </c>
       <c r="D7" t="n">
         <v>200</v>
       </c>
       <c r="E7" t="n">
-        <v>371</v>
+        <v>742</v>
       </c>
       <c r="F7" t="n">
-        <v>371.81</v>
+        <v>743.62</v>
       </c>
       <c r="G7" t="n">
-        <v>35.93746522829867</v>
+        <v>71.87493045659734</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -7593,19 +7593,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33.841</v>
+        <v>67.682</v>
       </c>
       <c r="D8" t="n">
         <v>173</v>
       </c>
       <c r="E8" t="n">
-        <v>186</v>
+        <v>372</v>
       </c>
       <c r="F8" t="n">
-        <v>194.5780346820809</v>
+        <v>389.1560693641619</v>
       </c>
       <c r="G8" t="n">
-        <v>31.27208024887077</v>
+        <v>62.54416049774154</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -7623,19 +7623,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.738</v>
+        <v>149.476</v>
       </c>
       <c r="D9" t="n">
         <v>187</v>
       </c>
       <c r="E9" t="n">
-        <v>401</v>
+        <v>802</v>
       </c>
       <c r="F9" t="n">
-        <v>397.6737967914439</v>
+        <v>795.3475935828877</v>
       </c>
       <c r="G9" t="n">
-        <v>70.08792870787832</v>
+        <v>140.1758574157566</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -7653,19 +7653,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74.84</v>
+        <v>149.68</v>
       </c>
       <c r="D10" t="n">
         <v>222</v>
       </c>
       <c r="E10" t="n">
-        <v>330.5</v>
+        <v>661</v>
       </c>
       <c r="F10" t="n">
-        <v>336.0810810810811</v>
+        <v>672.1621621621622</v>
       </c>
       <c r="G10" t="n">
-        <v>39.62188597984365</v>
+        <v>79.24377195968731</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -7683,19 +7683,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.41</v>
+        <v>150.82</v>
       </c>
       <c r="D11" t="n">
         <v>197</v>
       </c>
       <c r="E11" t="n">
-        <v>376</v>
+        <v>752</v>
       </c>
       <c r="F11" t="n">
-        <v>380.3502538071066</v>
+        <v>760.7005076142132</v>
       </c>
       <c r="G11" t="n">
-        <v>31.14816734603957</v>
+        <v>62.29633469207915</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -7713,19 +7713,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74.988</v>
+        <v>149.976</v>
       </c>
       <c r="D12" t="n">
         <v>240</v>
       </c>
       <c r="E12" t="n">
-        <v>286</v>
+        <v>572</v>
       </c>
       <c r="F12" t="n">
-        <v>311.0083333333333</v>
+        <v>622.0166666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>70.40504401782604</v>
+        <v>140.8100880356521</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -7743,19 +7743,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75.02</v>
+        <v>150.04</v>
       </c>
       <c r="D13" t="n">
         <v>279</v>
       </c>
       <c r="E13" t="n">
-        <v>267</v>
+        <v>534</v>
       </c>
       <c r="F13" t="n">
-        <v>268.3010752688172</v>
+        <v>536.6021505376344</v>
       </c>
       <c r="G13" t="n">
-        <v>19.9930482232426</v>
+        <v>39.98609644648521</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7773,19 +7773,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75.456</v>
+        <v>150.912</v>
       </c>
       <c r="D14" t="n">
         <v>203</v>
       </c>
       <c r="E14" t="n">
-        <v>356</v>
+        <v>712</v>
       </c>
       <c r="F14" t="n">
-        <v>370.8817733990148</v>
+        <v>741.7635467980296</v>
       </c>
       <c r="G14" t="n">
-        <v>124.3945169783027</v>
+        <v>248.7890339566053</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>74.845</v>
+        <v>149.69</v>
       </c>
       <c r="D15" t="n">
         <v>206</v>
       </c>
       <c r="E15" t="n">
-        <v>345.5</v>
+        <v>691</v>
       </c>
       <c r="F15" t="n">
-        <v>362.5145631067961</v>
+        <v>725.0291262135922</v>
       </c>
       <c r="G15" t="n">
-        <v>89.03163198660596</v>
+        <v>178.0632639732119</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -7833,19 +7833,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74.611</v>
+        <v>149.222</v>
       </c>
       <c r="D16" t="n">
         <v>203</v>
       </c>
       <c r="E16" t="n">
-        <v>368</v>
+        <v>736</v>
       </c>
       <c r="F16" t="n">
-        <v>365.3399014778325</v>
+        <v>730.679802955665</v>
       </c>
       <c r="G16" t="n">
-        <v>29.78516698404548</v>
+        <v>59.57033396809096</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -7863,19 +7863,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75.004</v>
+        <v>150.008</v>
       </c>
       <c r="D17" t="n">
         <v>170</v>
       </c>
       <c r="E17" t="n">
-        <v>436</v>
+        <v>872</v>
       </c>
       <c r="F17" t="n">
-        <v>433.0823529411765</v>
+        <v>866.1647058823529</v>
       </c>
       <c r="G17" t="n">
-        <v>99.46474642511866</v>
+        <v>198.9294928502373</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -7893,19 +7893,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36.692</v>
+        <v>73.384</v>
       </c>
       <c r="D18" t="n">
         <v>113</v>
       </c>
       <c r="E18" t="n">
-        <v>310</v>
+        <v>620</v>
       </c>
       <c r="F18" t="n">
-        <v>321.8849557522124</v>
+        <v>643.7699115044247</v>
       </c>
       <c r="G18" t="n">
-        <v>46.28864258502399</v>
+        <v>92.57728517004799</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -7923,19 +7923,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37.287</v>
+        <v>74.574</v>
       </c>
       <c r="D19" t="n">
         <v>177</v>
       </c>
       <c r="E19" t="n">
-        <v>179</v>
+        <v>358</v>
       </c>
       <c r="F19" t="n">
-        <v>209.6101694915254</v>
+        <v>419.2203389830509</v>
       </c>
       <c r="G19" t="n">
-        <v>54.74372637857253</v>
+        <v>109.4874527571451</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -7953,19 +7953,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>74.938</v>
+        <v>149.876</v>
       </c>
       <c r="D20" t="n">
         <v>192</v>
       </c>
       <c r="E20" t="n">
-        <v>393.5</v>
+        <v>787</v>
       </c>
       <c r="F20" t="n">
-        <v>389.15625</v>
+        <v>778.3125</v>
       </c>
       <c r="G20" t="n">
-        <v>63.45602065676371</v>
+        <v>126.9120413135274</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -7983,19 +7983,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>74.904</v>
+        <v>149.808</v>
       </c>
       <c r="D21" t="n">
         <v>195</v>
       </c>
       <c r="E21" t="n">
-        <v>381</v>
+        <v>762</v>
       </c>
       <c r="F21" t="n">
-        <v>382.3230769230769</v>
+        <v>764.6461538461539</v>
       </c>
       <c r="G21" t="n">
-        <v>58.13744140892791</v>
+        <v>116.2748828178558</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -8013,19 +8013,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>74.292</v>
+        <v>148.584</v>
       </c>
       <c r="D22" t="n">
         <v>207</v>
       </c>
       <c r="E22" t="n">
-        <v>347</v>
+        <v>694</v>
       </c>
       <c r="F22" t="n">
-        <v>358.1497584541063</v>
+        <v>716.2995169082126</v>
       </c>
       <c r="G22" t="n">
-        <v>75.79130638620619</v>
+        <v>151.5826127724124</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -8043,19 +8043,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.189</v>
+        <v>114.378</v>
       </c>
       <c r="D23" t="n">
         <v>126</v>
       </c>
       <c r="E23" t="n">
-        <v>449.5</v>
+        <v>899</v>
       </c>
       <c r="F23" t="n">
-        <v>449.6746031746032</v>
+        <v>899.3492063492064</v>
       </c>
       <c r="G23" t="n">
-        <v>75.0241379146823</v>
+        <v>150.0482758293646</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -8073,19 +8073,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74.851</v>
+        <v>149.702</v>
       </c>
       <c r="D24" t="n">
         <v>200</v>
       </c>
       <c r="E24" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="F24" t="n">
-        <v>372.06</v>
+        <v>744.12</v>
       </c>
       <c r="G24" t="n">
-        <v>58.94249305413868</v>
+        <v>117.8849861082774</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -8103,19 +8103,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.80500000000001</v>
+        <v>149.61</v>
       </c>
       <c r="D25" t="n">
         <v>198</v>
       </c>
       <c r="E25" t="n">
-        <v>359.5</v>
+        <v>719</v>
       </c>
       <c r="F25" t="n">
-        <v>376.3535353535353</v>
+        <v>752.7070707070707</v>
       </c>
       <c r="G25" t="n">
-        <v>98.29679631149128</v>
+        <v>196.5935926229826</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>74.867</v>
+        <v>149.734</v>
       </c>
       <c r="D26" t="n">
         <v>192</v>
       </c>
       <c r="E26" t="n">
-        <v>385</v>
+        <v>770</v>
       </c>
       <c r="F26" t="n">
-        <v>388.0729166666667</v>
+        <v>776.1458333333334</v>
       </c>
       <c r="G26" t="n">
-        <v>41.69177472124006</v>
+        <v>83.38354944248012</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -8163,19 +8163,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>74.995</v>
+        <v>149.99</v>
       </c>
       <c r="D27" t="n">
         <v>194</v>
       </c>
       <c r="E27" t="n">
-        <v>377</v>
+        <v>754</v>
       </c>
       <c r="F27" t="n">
-        <v>385.5</v>
+        <v>771</v>
       </c>
       <c r="G27" t="n">
-        <v>78.307038176522</v>
+        <v>156.614076353044</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -8193,19 +8193,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>51.061</v>
+        <v>102.122</v>
       </c>
       <c r="D28" t="n">
         <v>122</v>
       </c>
       <c r="E28" t="n">
-        <v>427</v>
+        <v>854</v>
       </c>
       <c r="F28" t="n">
-        <v>416.2786885245902</v>
+        <v>832.5573770491803</v>
       </c>
       <c r="G28" t="n">
-        <v>75.69853894406297</v>
+        <v>151.3970778881259</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -8223,19 +8223,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>75.146</v>
+        <v>150.292</v>
       </c>
       <c r="D29" t="n">
         <v>226</v>
       </c>
       <c r="E29" t="n">
-        <v>331</v>
+        <v>662</v>
       </c>
       <c r="F29" t="n">
-        <v>331.6106194690266</v>
+        <v>663.2212389380531</v>
       </c>
       <c r="G29" t="n">
-        <v>51.22853955075669</v>
+        <v>102.4570791015134</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -8253,19 +8253,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>75.042</v>
+        <v>150.084</v>
       </c>
       <c r="D30" t="n">
         <v>215</v>
       </c>
       <c r="E30" t="n">
-        <v>348</v>
+        <v>696</v>
       </c>
       <c r="F30" t="n">
-        <v>348.1813953488372</v>
+        <v>696.3627906976744</v>
       </c>
       <c r="G30" t="n">
-        <v>32.46363354149995</v>
+        <v>64.9272670829999</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -8283,19 +8283,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>75.004</v>
+        <v>150.008</v>
       </c>
       <c r="D31" t="n">
         <v>189</v>
       </c>
       <c r="E31" t="n">
-        <v>404</v>
+        <v>808</v>
       </c>
       <c r="F31" t="n">
-        <v>395.5978835978836</v>
+        <v>791.1957671957672</v>
       </c>
       <c r="G31" t="n">
-        <v>104.8984676062301</v>
+        <v>209.7969352124603</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -8313,19 +8313,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>74.98399999999999</v>
+        <v>149.968</v>
       </c>
       <c r="D32" t="n">
         <v>239</v>
       </c>
       <c r="E32" t="n">
-        <v>312</v>
+        <v>624</v>
       </c>
       <c r="F32" t="n">
-        <v>312.5523012552301</v>
+        <v>625.1046025104603</v>
       </c>
       <c r="G32" t="n">
-        <v>35.28200294876881</v>
+        <v>70.56400589753763</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -8343,19 +8343,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>74.904</v>
+        <v>149.808</v>
       </c>
       <c r="D33" t="n">
         <v>237</v>
       </c>
       <c r="E33" t="n">
-        <v>314</v>
+        <v>628</v>
       </c>
       <c r="F33" t="n">
-        <v>314.4810126582278</v>
+        <v>628.9620253164557</v>
       </c>
       <c r="G33" t="n">
-        <v>24.13900112352134</v>
+        <v>48.27800224704268</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -8373,19 +8373,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>71.206</v>
+        <v>142.412</v>
       </c>
       <c r="D34" t="n">
         <v>187</v>
       </c>
       <c r="E34" t="n">
-        <v>373</v>
+        <v>746</v>
       </c>
       <c r="F34" t="n">
-        <v>379.2513368983957</v>
+        <v>758.5026737967914</v>
       </c>
       <c r="G34" t="n">
-        <v>66.00192189959057</v>
+        <v>132.0038437991811</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -8403,19 +8403,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>74.81999999999999</v>
+        <v>149.64</v>
       </c>
       <c r="D35" t="n">
         <v>167</v>
       </c>
       <c r="E35" t="n">
-        <v>449</v>
+        <v>898</v>
       </c>
       <c r="F35" t="n">
-        <v>445.6407185628743</v>
+        <v>891.2814371257485</v>
       </c>
       <c r="G35" t="n">
-        <v>24.56101857039925</v>
+        <v>49.1220371407985</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -8433,19 +8433,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>75.093</v>
+        <v>150.186</v>
       </c>
       <c r="D36" t="n">
         <v>235</v>
       </c>
       <c r="E36" t="n">
-        <v>317</v>
+        <v>634</v>
       </c>
       <c r="F36" t="n">
-        <v>318.5829787234043</v>
+        <v>637.1659574468085</v>
       </c>
       <c r="G36" t="n">
-        <v>20.92141706347803</v>
+        <v>41.84283412695606</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -8463,19 +8463,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>74.926</v>
+        <v>149.852</v>
       </c>
       <c r="D37" t="n">
         <v>216</v>
       </c>
       <c r="E37" t="n">
-        <v>322.5</v>
+        <v>645</v>
       </c>
       <c r="F37" t="n">
-        <v>345.087962962963</v>
+        <v>690.175925925926</v>
       </c>
       <c r="G37" t="n">
-        <v>95.66927840837945</v>
+        <v>191.3385568167589</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -8493,19 +8493,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>75.11199999999999</v>
+        <v>150.224</v>
       </c>
       <c r="D38" t="n">
         <v>181</v>
       </c>
       <c r="E38" t="n">
-        <v>395</v>
+        <v>790</v>
       </c>
       <c r="F38" t="n">
-        <v>413.585635359116</v>
+        <v>827.171270718232</v>
       </c>
       <c r="G38" t="n">
-        <v>135.8362560555075</v>
+        <v>271.6725121110151</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -8523,19 +8523,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>75.024</v>
+        <v>150.048</v>
       </c>
       <c r="D39" t="n">
         <v>204</v>
       </c>
       <c r="E39" t="n">
-        <v>362.5</v>
+        <v>725</v>
       </c>
       <c r="F39" t="n">
-        <v>365.9362745098039</v>
+        <v>731.8725490196078</v>
       </c>
       <c r="G39" t="n">
-        <v>28.81503537885845</v>
+        <v>57.63007075771691</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -8553,19 +8553,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>74.956</v>
+        <v>149.912</v>
       </c>
       <c r="D40" t="n">
         <v>275</v>
       </c>
       <c r="E40" t="n">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="F40" t="n">
-        <v>271.1781818181818</v>
+        <v>542.3563636363637</v>
       </c>
       <c r="G40" t="n">
-        <v>59.91893151873108</v>
+        <v>119.8378630374622</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -8583,19 +8583,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>74.982</v>
+        <v>149.964</v>
       </c>
       <c r="D41" t="n">
         <v>229</v>
       </c>
       <c r="E41" t="n">
-        <v>324</v>
+        <v>648</v>
       </c>
       <c r="F41" t="n">
-        <v>326.0960698689956</v>
+        <v>652.1921397379913</v>
       </c>
       <c r="G41" t="n">
-        <v>40.99229102017618</v>
+        <v>81.98458204035235</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -8613,19 +8613,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>72.312</v>
+        <v>144.624</v>
       </c>
       <c r="D42" t="n">
         <v>131</v>
       </c>
       <c r="E42" t="n">
-        <v>541</v>
+        <v>1082</v>
       </c>
       <c r="F42" t="n">
-        <v>548.412213740458</v>
+        <v>1096.824427480916</v>
       </c>
       <c r="G42" t="n">
-        <v>153.48685086397</v>
+        <v>306.9737017279401</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -8643,19 +8643,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>74.492</v>
+        <v>148.984</v>
       </c>
       <c r="D43" t="n">
         <v>182</v>
       </c>
       <c r="E43" t="n">
-        <v>393</v>
+        <v>786</v>
       </c>
       <c r="F43" t="n">
-        <v>407.3076923076923</v>
+        <v>814.6153846153846</v>
       </c>
       <c r="G43" t="n">
-        <v>137.6591348188162</v>
+        <v>275.3182696376325</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -8673,19 +8673,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>74.691</v>
+        <v>149.382</v>
       </c>
       <c r="D44" t="n">
         <v>195</v>
       </c>
       <c r="E44" t="n">
-        <v>376</v>
+        <v>752</v>
       </c>
       <c r="F44" t="n">
-        <v>379.574358974359</v>
+        <v>759.1487179487179</v>
       </c>
       <c r="G44" t="n">
-        <v>74.4897305519729</v>
+        <v>148.9794611039458</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -8703,19 +8703,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34.005</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="D45" t="n">
         <v>92</v>
       </c>
       <c r="E45" t="n">
-        <v>369</v>
+        <v>738</v>
       </c>
       <c r="F45" t="n">
-        <v>364.7717391304348</v>
+        <v>729.5434782608696</v>
       </c>
       <c r="G45" t="n">
-        <v>29.08347337089941</v>
+        <v>58.16694674179881</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -8733,19 +8733,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>74.935</v>
+        <v>149.87</v>
       </c>
       <c r="D46" t="n">
         <v>189</v>
       </c>
       <c r="E46" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="F46" t="n">
-        <v>394.5079365079365</v>
+        <v>789.015873015873</v>
       </c>
       <c r="G46" t="n">
-        <v>23.1226192673577</v>
+        <v>46.24523853471539</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -8763,19 +8763,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>75.092</v>
+        <v>150.184</v>
       </c>
       <c r="D47" t="n">
         <v>193</v>
       </c>
       <c r="E47" t="n">
-        <v>390</v>
+        <v>780</v>
       </c>
       <c r="F47" t="n">
-        <v>387.2849740932642</v>
+        <v>774.5699481865284</v>
       </c>
       <c r="G47" t="n">
-        <v>30.03273616899067</v>
+        <v>60.06547233798134</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -8793,19 +8793,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>75.01900000000001</v>
+        <v>150.038</v>
       </c>
       <c r="D48" t="n">
         <v>206</v>
       </c>
       <c r="E48" t="n">
-        <v>363</v>
+        <v>726</v>
       </c>
       <c r="F48" t="n">
-        <v>362.9174757281554</v>
+        <v>725.8349514563107</v>
       </c>
       <c r="G48" t="n">
-        <v>25.3390277488207</v>
+        <v>50.6780554976414</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -8823,19 +8823,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>74.947</v>
+        <v>149.894</v>
       </c>
       <c r="D49" t="n">
         <v>211</v>
       </c>
       <c r="E49" t="n">
-        <v>352</v>
+        <v>704</v>
       </c>
       <c r="F49" t="n">
-        <v>353.6445497630332</v>
+        <v>707.2890995260664</v>
       </c>
       <c r="G49" t="n">
-        <v>16.60440865614102</v>
+        <v>33.20881731228204</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -8853,19 +8853,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>69.142</v>
+        <v>138.284</v>
       </c>
       <c r="D50" t="n">
         <v>201</v>
       </c>
       <c r="E50" t="n">
-        <v>321</v>
+        <v>642</v>
       </c>
       <c r="F50" t="n">
-        <v>342.9651741293532</v>
+        <v>685.9303482587064</v>
       </c>
       <c r="G50" t="n">
-        <v>81.11247611246083</v>
+        <v>162.2249522249217</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -8883,19 +8883,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>31.918</v>
+        <v>63.836</v>
       </c>
       <c r="D51" t="n">
         <v>95</v>
       </c>
       <c r="E51" t="n">
-        <v>329</v>
+        <v>658</v>
       </c>
       <c r="F51" t="n">
-        <v>332.7052631578948</v>
+        <v>665.4105263157895</v>
       </c>
       <c r="G51" t="n">
-        <v>35.97867976366551</v>
+        <v>71.95735952733102</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -8913,19 +8913,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>74.97199999999999</v>
+        <v>149.944</v>
       </c>
       <c r="D52" t="n">
         <v>221</v>
       </c>
       <c r="E52" t="n">
-        <v>338</v>
+        <v>676</v>
       </c>
       <c r="F52" t="n">
-        <v>337.9547511312217</v>
+        <v>675.9095022624434</v>
       </c>
       <c r="G52" t="n">
-        <v>43.46302229331965</v>
+        <v>86.92604458663929</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -8943,19 +8943,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>74.809</v>
+        <v>149.618</v>
       </c>
       <c r="D53" t="n">
         <v>198</v>
       </c>
       <c r="E53" t="n">
-        <v>354</v>
+        <v>708</v>
       </c>
       <c r="F53" t="n">
-        <v>375.7777777777778</v>
+        <v>751.5555555555555</v>
       </c>
       <c r="G53" t="n">
-        <v>81.93318505532892</v>
+        <v>163.8663701106578</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -8973,19 +8973,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68.699</v>
+        <v>137.398</v>
       </c>
       <c r="D54" t="n">
         <v>196</v>
       </c>
       <c r="E54" t="n">
-        <v>344.5</v>
+        <v>689</v>
       </c>
       <c r="F54" t="n">
-        <v>349.5510204081633</v>
+        <v>699.1020408163265</v>
       </c>
       <c r="G54" t="n">
-        <v>46.862181449816</v>
+        <v>93.724362899632</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -9003,19 +9003,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>74.813</v>
+        <v>149.626</v>
       </c>
       <c r="D55" t="n">
         <v>239</v>
       </c>
       <c r="E55" t="n">
-        <v>309</v>
+        <v>618</v>
       </c>
       <c r="F55" t="n">
-        <v>311.7698744769875</v>
+        <v>623.5397489539749</v>
       </c>
       <c r="G55" t="n">
-        <v>22.65788147292947</v>
+        <v>45.31576294585894</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -9033,19 +9033,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67.78</v>
+        <v>135.56</v>
       </c>
       <c r="D56" t="n">
         <v>170</v>
       </c>
       <c r="E56" t="n">
-        <v>395</v>
+        <v>790</v>
       </c>
       <c r="F56" t="n">
-        <v>397.2411764705882</v>
+        <v>794.4823529411765</v>
       </c>
       <c r="G56" t="n">
-        <v>61.85175595392631</v>
+        <v>123.7035119078526</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -9063,19 +9063,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>75.039</v>
+        <v>150.078</v>
       </c>
       <c r="D57" t="n">
         <v>201</v>
       </c>
       <c r="E57" t="n">
-        <v>372</v>
+        <v>744</v>
       </c>
       <c r="F57" t="n">
-        <v>371.5422885572139</v>
+        <v>743.0845771144278</v>
       </c>
       <c r="G57" t="n">
-        <v>46.75392446347492</v>
+        <v>93.50784892694983</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -9093,19 +9093,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>74.875</v>
+        <v>149.75</v>
       </c>
       <c r="D58" t="n">
         <v>237</v>
       </c>
       <c r="E58" t="n">
-        <v>312</v>
+        <v>624</v>
       </c>
       <c r="F58" t="n">
-        <v>314.1856540084388</v>
+        <v>628.3713080168776</v>
       </c>
       <c r="G58" t="n">
-        <v>42.92424501688542</v>
+        <v>85.84849003377084</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -9123,19 +9123,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>74.901</v>
+        <v>149.802</v>
       </c>
       <c r="D59" t="n">
         <v>199</v>
       </c>
       <c r="E59" t="n">
-        <v>369</v>
+        <v>738</v>
       </c>
       <c r="F59" t="n">
-        <v>374.4070351758794</v>
+        <v>748.8140703517588</v>
       </c>
       <c r="G59" t="n">
-        <v>43.43263855294165</v>
+        <v>86.86527710588331</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -9153,19 +9153,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>61.086</v>
+        <v>122.172</v>
       </c>
       <c r="D60" t="n">
         <v>177</v>
       </c>
       <c r="E60" t="n">
-        <v>329</v>
+        <v>658</v>
       </c>
       <c r="F60" t="n">
-        <v>343.9887005649717</v>
+        <v>687.9774011299435</v>
       </c>
       <c r="G60" t="n">
-        <v>65.02228540177633</v>
+        <v>130.0445708035527</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -9183,19 +9183,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>75.426</v>
+        <v>150.852</v>
       </c>
       <c r="D61" t="n">
         <v>215</v>
       </c>
       <c r="E61" t="n">
-        <v>348</v>
+        <v>696</v>
       </c>
       <c r="F61" t="n">
-        <v>348.7674418604651</v>
+        <v>697.5348837209302</v>
       </c>
       <c r="G61" t="n">
-        <v>29.05701550344423</v>
+        <v>58.11403100688846</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -9213,19 +9213,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>74.711</v>
+        <v>149.422</v>
       </c>
       <c r="D62" t="n">
         <v>238</v>
       </c>
       <c r="E62" t="n">
-        <v>309</v>
+        <v>618</v>
       </c>
       <c r="F62" t="n">
-        <v>312.781512605042</v>
+        <v>625.563025210084</v>
       </c>
       <c r="G62" t="n">
-        <v>20.53982841429962</v>
+        <v>41.07965682859924</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -9243,19 +9243,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>74.803</v>
+        <v>149.606</v>
       </c>
       <c r="D63" t="n">
         <v>219</v>
       </c>
       <c r="E63" t="n">
-        <v>337</v>
+        <v>674</v>
       </c>
       <c r="F63" t="n">
-        <v>339.8493150684931</v>
+        <v>679.6986301369863</v>
       </c>
       <c r="G63" t="n">
-        <v>27.10225517862395</v>
+        <v>54.20451035724791</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -9273,19 +9273,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>93.08199999999999</v>
+        <v>186.164</v>
       </c>
       <c r="D64" t="n">
         <v>229</v>
       </c>
       <c r="E64" t="n">
-        <v>406</v>
+        <v>812</v>
       </c>
       <c r="F64" t="n">
-        <v>404.8078602620087</v>
+        <v>809.6157205240174</v>
       </c>
       <c r="G64" t="n">
-        <v>60.66522840924033</v>
+        <v>121.3304568184807</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -9303,19 +9303,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>22.515</v>
+        <v>45.03</v>
       </c>
       <c r="D65" t="n">
         <v>55</v>
       </c>
       <c r="E65" t="n">
-        <v>388</v>
+        <v>776</v>
       </c>
       <c r="F65" t="n">
-        <v>400.2181818181818</v>
+        <v>800.4363636363636</v>
       </c>
       <c r="G65" t="n">
-        <v>72.2271855326395</v>
+        <v>144.454371065279</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -9333,19 +9333,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>70.85299999999999</v>
+        <v>141.706</v>
       </c>
       <c r="D66" t="n">
         <v>191</v>
       </c>
       <c r="E66" t="n">
-        <v>363</v>
+        <v>726</v>
       </c>
       <c r="F66" t="n">
-        <v>368.17277486911</v>
+        <v>736.3455497382199</v>
       </c>
       <c r="G66" t="n">
-        <v>49.39653186362695</v>
+        <v>98.79306372725389</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -9363,19 +9363,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>75.375</v>
+        <v>150.75</v>
       </c>
       <c r="D67" t="n">
         <v>257</v>
       </c>
       <c r="E67" t="n">
-        <v>289</v>
+        <v>578</v>
       </c>
       <c r="F67" t="n">
-        <v>291.9610894941634</v>
+        <v>583.9221789883269</v>
       </c>
       <c r="G67" t="n">
-        <v>23.52771063147381</v>
+        <v>47.05542126294762</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -9393,19 +9393,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>60.649</v>
+        <v>121.298</v>
       </c>
       <c r="D68" t="n">
         <v>168</v>
       </c>
       <c r="E68" t="n">
-        <v>359.5</v>
+        <v>719</v>
       </c>
       <c r="F68" t="n">
-        <v>359.6666666666667</v>
+        <v>719.3333333333334</v>
       </c>
       <c r="G68" t="n">
-        <v>31.89610128910914</v>
+        <v>63.79220257821829</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -9423,19 +9423,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>54.225</v>
+        <v>108.45</v>
       </c>
       <c r="D69" t="n">
         <v>142</v>
       </c>
       <c r="E69" t="n">
-        <v>377.5</v>
+        <v>755</v>
       </c>
       <c r="F69" t="n">
-        <v>380.1549295774648</v>
+        <v>760.3098591549295</v>
       </c>
       <c r="G69" t="n">
-        <v>58.1982788094114</v>
+        <v>116.3965576188228</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -9453,19 +9453,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>41.858</v>
+        <v>83.71599999999999</v>
       </c>
       <c r="D70" t="n">
         <v>106</v>
       </c>
       <c r="E70" t="n">
-        <v>381</v>
+        <v>762</v>
       </c>
       <c r="F70" t="n">
-        <v>391.1415094339623</v>
+        <v>782.2830188679245</v>
       </c>
       <c r="G70" t="n">
-        <v>85.51919179528628</v>
+        <v>171.0383835905726</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -9483,19 +9483,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>75.336</v>
+        <v>150.672</v>
       </c>
       <c r="D71" t="n">
         <v>211</v>
       </c>
       <c r="E71" t="n">
-        <v>356</v>
+        <v>712</v>
       </c>
       <c r="F71" t="n">
-        <v>356.0616113744076</v>
+        <v>712.1232227488151</v>
       </c>
       <c r="G71" t="n">
-        <v>28.8968773277645</v>
+        <v>57.793754655529</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -9513,19 +9513,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>74.992</v>
+        <v>149.984</v>
       </c>
       <c r="D72" t="n">
         <v>185</v>
       </c>
       <c r="E72" t="n">
-        <v>407</v>
+        <v>814</v>
       </c>
       <c r="F72" t="n">
-        <v>404.2378378378378</v>
+        <v>808.4756756756757</v>
       </c>
       <c r="G72" t="n">
-        <v>59.00089973223028</v>
+        <v>118.0017994644606</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -9543,19 +9543,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>52.248</v>
+        <v>104.496</v>
       </c>
       <c r="D73" t="n">
         <v>117</v>
       </c>
       <c r="E73" t="n">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="F73" t="n">
-        <v>441.3162393162393</v>
+        <v>882.6324786324786</v>
       </c>
       <c r="G73" t="n">
-        <v>149.5440570287963</v>
+        <v>299.0881140575926</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -9573,19 +9573,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>74.694</v>
+        <v>149.388</v>
       </c>
       <c r="D74" t="n">
         <v>213</v>
       </c>
       <c r="E74" t="n">
-        <v>346</v>
+        <v>692</v>
       </c>
       <c r="F74" t="n">
-        <v>349.8169014084507</v>
+        <v>699.6338028169014</v>
       </c>
       <c r="G74" t="n">
-        <v>57.82634458522595</v>
+        <v>115.6526891704519</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -9603,19 +9603,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74.742</v>
+        <v>149.484</v>
       </c>
       <c r="D75" t="n">
         <v>184</v>
       </c>
       <c r="E75" t="n">
-        <v>399</v>
+        <v>798</v>
       </c>
       <c r="F75" t="n">
-        <v>404.1304347826087</v>
+        <v>808.2608695652174</v>
       </c>
       <c r="G75" t="n">
-        <v>50.96623062666892</v>
+        <v>101.9324612533378</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -9633,19 +9633,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>74.999</v>
+        <v>149.998</v>
       </c>
       <c r="D76" t="n">
         <v>235</v>
       </c>
       <c r="E76" t="n">
-        <v>317</v>
+        <v>634</v>
       </c>
       <c r="F76" t="n">
-        <v>317.4382978723404</v>
+        <v>634.8765957446808</v>
       </c>
       <c r="G76" t="n">
-        <v>22.51171160715112</v>
+        <v>45.02342321430224</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -9663,19 +9663,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>74.761</v>
+        <v>149.522</v>
       </c>
       <c r="D77" t="n">
         <v>166</v>
       </c>
       <c r="E77" t="n">
-        <v>451</v>
+        <v>902</v>
       </c>
       <c r="F77" t="n">
-        <v>447.2650602409639</v>
+        <v>894.5301204819277</v>
       </c>
       <c r="G77" t="n">
-        <v>49.357344935554</v>
+        <v>98.71468987110799</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -9693,19 +9693,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>129.117</v>
+        <v>258.234</v>
       </c>
       <c r="D78" t="n">
         <v>317</v>
       </c>
       <c r="E78" t="n">
-        <v>407</v>
+        <v>814</v>
       </c>
       <c r="F78" t="n">
-        <v>405.9053627760252</v>
+        <v>811.8107255520505</v>
       </c>
       <c r="G78" t="n">
-        <v>49.71943946810985</v>
+        <v>99.43887893621971</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
